--- a/회의록.xlsx
+++ b/회의록.xlsx
@@ -4,20 +4,23 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="회의록 원본" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="20261022 오후" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="20261022오전" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="20261020" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="20261019" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="20261016" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="20261015" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="20261014" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="20261013" sheetId="9" r:id="rId13"/>
-    <sheet state="visible" name="20261008" sheetId="10" r:id="rId14"/>
-    <sheet state="visible" name="20261006" sheetId="11" r:id="rId15"/>
-    <sheet state="visible" name="20261002" sheetId="12" r:id="rId16"/>
-    <sheet state="visible" name="20261001" sheetId="13" r:id="rId17"/>
-    <sheet state="visible" name="20260929" sheetId="14" r:id="rId18"/>
-    <sheet state="visible" name="20260923" sheetId="15" r:id="rId19"/>
+    <sheet state="visible" name="20261028" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="20261027" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="20261026" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="20261022 오후" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="20261022오전" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="20261020" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="20261019" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="20261016" sheetId="9" r:id="rId13"/>
+    <sheet state="visible" name="20261015" sheetId="10" r:id="rId14"/>
+    <sheet state="visible" name="20261014" sheetId="11" r:id="rId15"/>
+    <sheet state="visible" name="20261013" sheetId="12" r:id="rId16"/>
+    <sheet state="visible" name="20261008" sheetId="13" r:id="rId17"/>
+    <sheet state="visible" name="20261006" sheetId="14" r:id="rId18"/>
+    <sheet state="visible" name="20261002" sheetId="15" r:id="rId19"/>
+    <sheet state="visible" name="20261001" sheetId="16" r:id="rId20"/>
+    <sheet state="visible" name="20260929" sheetId="17" r:id="rId21"/>
+    <sheet state="visible" name="20260923" sheetId="18" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="172">
   <si>
     <t>참고자료</t>
   </si>
@@ -33,106 +36,292 @@
     <t>회의명</t>
   </si>
   <si>
-    <t>TRD, PRD, 기타 문서 확인</t>
-  </si>
-  <si>
-    <t>기능관련 회의</t>
-  </si>
-  <si>
     <t>회의 유형</t>
   </si>
   <si>
-    <t>서류작업 회의</t>
-  </si>
-  <si>
     <t>회의 일시</t>
   </si>
   <si>
+    <t>PRD 피드백 및 업무 시간 분배에 대한 회의</t>
+  </si>
+  <si>
+    <t>참석자</t>
+  </si>
+  <si>
+    <t>작성자</t>
+  </si>
+  <si>
+    <t>회의목적</t>
+  </si>
+  <si>
+    <t>피드백 회의</t>
+  </si>
+  <si>
+    <t>요약</t>
+  </si>
+  <si>
+    <t>2026-10-28 10:20~11:30, 15:00~16:00</t>
+  </si>
+  <si>
+    <t>주요 내용</t>
+  </si>
+  <si>
+    <t>지웅, 성준, 진희, 소현, 혜현</t>
+  </si>
+  <si>
+    <t>진희</t>
+  </si>
+  <si>
+    <t>업무에 대한 피드백</t>
+  </si>
+  <si>
+    <t>앞으로 해야할 일</t>
+  </si>
+  <si>
+    <t>일정 데드라인</t>
+  </si>
+  <si>
+    <t>아직 해소되지 
+ 않은 사항</t>
+  </si>
+  <si>
+    <t>노트</t>
+  </si>
+  <si>
+    <t>팀장님 코멘트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+1. WBS에 대한 내용. 
+- 우리가 업무에 대해서 확실한 순서를 확인할 필요가 있음.
+- 업무를 언제까지 해야할지 감을 잡아야 할 필요가 있음. 
+- 그렇기에 WBS를 작성할 필요가 있음. 
+이리저리해서 요약
+~10/30(금)        기능정의서, 시나리오 기획서, TRD, 기술 아키텍처, 화면정의서 초안. API 명세서는 1차본(엔드포인트 목록과 주요 필드)
+11/2~11/6        ERD, 테이블 정의서(월~화에 우선), AI 아키텍처, 프롬프트, API 명세서 확정, 테스트 계획서. 11/6에 범위와 명세 동결
+11/9~11/17        개발 본격 진행. 테스트 케이스와 매뉴얼 초안은 개발과 병행
+11/16~11/19        QA와 버그 수정, 매뉴얼에 스크린샷 반영
+11/20(금)        산출물 확정 (버퍼를 겸함)
+11/21~27        발표자료 제작과 리허설, 11/27 제출
+- 역할에 대한 재산출- 역할비중이 너무 쏠리지 않게끔.
+* 오늘 오전작업 &gt; PRD 소현님이 작성한 거 검토 후, 피드백을 주기로.
+-지웅님이 정리하는데 고생하심. 
+- WBS 업무에 대해서 이전에 작성한거 활용하자는 이야기가 의견&gt; 일부 반영(아마 현재 우리가 하고 있는 기준하고 잘 맞지 않은 것으로 추측
+2. 문서대장 관련 정리.
+날짜 정확히 어떻게하고, 역할을 다시 정립하고 올림.
+3. FASTAPI에 대한 성준님의 강의
+- 코드량이 단축된 API를 정의함.
+- 연걸하기 편리함.
+-Pydantic이 지원되는 특징.
+- Api서버를 만들기 쉽게 되어있음.
+API에 대한 비유
+손님&gt; 프론트엔드, 메뉴판&gt;API명세, 주문&gt;요청(req), 주방&gt;벡엔드서버(실제처리로직),음식&gt;응답(resp)
+우리가 논의 해야할 부분.
+엔드포인트의 목적 url http 무엇인가
+요청 본문에 어떤 필드가 필요한가, 필수선택 여부와 데이터 타입.
+성공했을 때 어떤 응답 JSON을 돌려줄 것인지.
+실패할 수 있는 경우와 상태코드
+로그인 권한 확인, 필요한 API
+API를 누가 구현하고 어떻게 테스트
+4.PRD에 대한 피드백.
+1.  1차는 관리자가 직접 관여 안하고 합 / 불합 체크. 무조건(60점~70점) &gt; 평가 시스템
+2. 계정가입 문제? &gt;&gt; test email일때, 어떻게 반응할지?(이거는 실제로 한다면, 이메일인증을 하긴함.)
+&gt;&gt;이메일 인증하기로.(초반에 우리가 걱정할 일은 아니라고 생각함.)
+3. VRAM 24GB,&gt;&gt; 그냥 메모리 
+VRAM은 6기가 
+RAM은 56기가
+사실 이게 테스트 기준으로 해서 만드는 거라 실제 업무에서는 더 큰 스펙으로 진행이 되고있다고 명시하는게 맞음. 
+벤치마킹 테스트&gt; 누가 결과가 빨리 나올지에 대한 기준으로 우리가 구현 이후 테스트 프로젝트로 선정.
+4. 재시도횟수, : 질문을 못만들어낼경우. 횟수가 다른 경우 산정, 그리고 재시도 횟수가 지났을 경우 어떻게 대처할 것인가.
+-&gt; 질문은행에서 랜덤으로 가져오기. 
+5.최대 2명으로 하되- 테스트해보고 , 알아보기. -PRD- 제한인원을 둔다. n명으로 두고. 사양에 따라서 움직이게끔.
+* LLM의 실수나 오류에 대한 내용. &gt; 우리가 LLM을 잘만드는 것도 중요하지만, 만에하나 실수하는 경우를 대비하는 것도 중요.
+이에 대한 대처법도 생각해놓자.</t>
+  </si>
+  <si>
+    <t>10/30(금)        기능정의서, 시나리오 기획서, TRD, 기술 아키텍처, 화면정의서 초안. API 명세서는 1차본</t>
+  </si>
+  <si>
+    <t>PRD 관련해서 어떻게 해야할지에 대한 회의</t>
+  </si>
+  <si>
+    <t>PRD 작성 이후 관련 토의</t>
+  </si>
+  <si>
+    <t>정기회의 + 팀의 방향을 잡아가는 회의</t>
+  </si>
+  <si>
+    <t>2026-10-27 10:20~ 11:10</t>
+  </si>
+  <si>
+    <t># AI 채용 플랫폼 PRD 4종 공통점 요약
+## 1. 공통 목적
+기업의 1차 채용 과정을 AI로 자동화하고, 표준화된 평가 기준을 통해 채용 담당자의 의사결정을 지원하는 플랫폼 구축.
+## 2. 핵심 공통 기능
+1. 사용자 관리: 지원자·관리자 로그인, 회원가입, 권한 구분
+2. 채용공고: 공고 등록·수정·조회, 지원 접수 및 관리
+3. 이력서: PDF 업로드, 직접 작성, 정보 추출 및 면접 질문 연계
+4. 질문 생성: 질문은행, 직무·이력서 기반 AI 질문 및 꼬리질문
+5. AI 면접: STT/TTS, 음성 답변, 자막, 제한시간, 진행 상태 관리
+6. 코딩테스트: 코드 작성·실행·제출·자동 채점
+7. AI 평가: 루브릭, 항목별 가중치, 점수 산출 및 평가 근거
+8. 결과 리포트: 종합 평가, 질문별 평가, 강점·개선점
+9. 관리자 기능: 공고·지원자 관리, 평가 검토, 최종 채용 결정
+10. 보안: 개인정보 동의, 접근 권한 관리, 온프레미스 AI 처리 지향
+## 3. 공통 서비스 흐름
+로그인/회원가입 -&gt; 채용공고 확인 → 지원 및 이력서 제출 → 면접 환경 점검 → AI 면접 → 코딩테스트 → AI 평가 및 리포트 → 관리자 검토 → 최종 채용 결정
+## 4. 공통 설계 원칙
+- 기업 채용을 위한 서비스
+- 직무·이력서 기반 맞춤형 질문 생성
+- 답변에 따른 AI 꼬리질문
+- 루브릭과 평가 근거를 활용한 평가 표준화
+- 지원자와 관리자의 정보 접근 권한 구분
+- 개인정보 보호 및 자체 AI 처리 환경 지향
+- AI는 평가를 보조하며 최종 채용 결정은 담당자가 수행
+## 5. 별도 합의가 필요한 사항
+- 면접 질문 수와 질문 구성
+- 응시 횟수 및 중단·재개 정책
+- 코딩테스트 AI 활용·평가 범위
+- 지원자에게 공개할 평가 정보와 시점
+- 평가 항목별 배점 및 총점 계산 방식
+- OCR, 시선 추적 등 부가 기능의 MVP 포함 여부
+- 실제 서버 사양 및 동시 응시 제한
+## 결론
+네 PRD는 기업의 채용공고와 지원자 정보를 기반으로 AI 면접 및 코딩테스트를 수행하고, 루브릭 기반 평가 결과를 제공하여 채용 담당자의 최종 의사결정을 지원한다는 공통 목적을 가진다. 다만 세부 운영 정책과 구현 범위는 추가 합의가 필요하다.</t>
+  </si>
+  <si>
+    <t>지웅,성준,진희,소현,혜현</t>
+  </si>
+  <si>
+    <t>팀의 방향 잡아가기.</t>
+  </si>
+  <si>
+    <t>서류작성의 경우 팀에서 함께 조율하며 담당하기.</t>
+  </si>
+  <si>
+    <t>구체적인 기획 회의</t>
+  </si>
+  <si>
+    <t>2026-10-26 16:30 ~ 18:30</t>
+  </si>
+  <si>
+    <t>PRD 작성관련 회의 및 역할분담에 관한 내용.</t>
+  </si>
+  <si>
+    <t>PRD 다시...써야겠지..?
+성준 RE : ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 진희의 오전 한마디(?)
+- 요약: 팀으로 할건지, 개인으로 할건지 확실히 정하자.
+- 결론 : 팀으로 서류작업을 처리하자.
+- 조건 : 팀이 하는 결론에 대해서 모두가 이의가 없도록.(이미 결론이 난 사항에 대해서는)
+- 조건2 : 진행중에 있는 불만에 대해서는 확실히 이야기해서 해소할 수 있도록.
+- 조건3 : 서류간 문제가 있을 경우 담당자간 확인 후 조율 후 진행(1차 담당자간-&gt; 2차 팀원전체)
+2. 성준의 모두의 것을 합친 PRD
+- 이어서 PRD 담당자(정:소현, 부:지웅)이 진행.
+- 검토 후에 초안을 내고, 팀원들의 검토가 필요.
+- 토큰 분배 필요할듯. 
+=&gt; 문서를 다루는데에는 크게 문제가 없었지만, 실제 구현 단계에서 문제가 됨
+- 그래서 정부 따로 진행하기로 함.
+3. 서류 리스트 및 서류 담당자 진행.
+- 전체적인 책임자. 책임자가 해당 서류에 대한 의견을 남길 수 있도록.
+- 마감일자 지정. 오늘 플로우차트 완성(혜현,진희) , WBS(지웅,진희,혜현)
+- 내일 PRD(소현,지웅), TRD(성준,소현), 화면정의서(진희,혜현)
+4. 이후 팀장회의에 갔음.
+내용 요약: 팀과 개인간의 어떻게 해야할지 방향잡기, 팀별로 어떻게 하기로 결정했는지.
+추가제안: 
+매일 회의에 작성이 완료된 서류를 검토하고(사전에 읽어오기) 문제점들을 체크하고 담당자의 버전업 시키기.
+추가 오후 회의:
+성준&amp;소현 - PRD관련 이야기 도중 중간에 평가기준에 대해서 간단히라도 지원자에게 공개하는 문구에 대한 내용 이야기
+질문에 대한 체크 - 우리가 질문을 만들때 어떻게 만드는지에 대한 재정립- 벡터DB? 질문은행? 이에 대한 방향을 확실히 잡아감.
+꼬리질문에 대한 내용- 어떨때 꼬리질문을 불러오는지에 대한 내용.
+LLM활용에 있어서 질문활용- 괜찮은 질문에 대한 정의 </t>
+  </si>
+  <si>
+    <t>팀장님 결정사항 공유</t>
+  </si>
+  <si>
+    <t xml:space="preserve">플로우차트, WBS(오늘까지) PRD,TRD,화면정의서(내일까지) </t>
+  </si>
+  <si>
+    <t>1 혜현님의 API 강의
+1. Endpoint와 url은 비슷함.
+2. 메서드는 대문자로 쓰긴함. 코드는 혼용 "@"를 넣어서 활용
+GET 조회
+POST 생성
+PUT FETCH 수정
+DELETE 삭제
+3. API는 json을 통해서 주고 받는다.
+4. 목록조회, 예약상세조회. 
+왜 상세조회에서는 POST인가?
+제이슨으로 데이터를 보내기 때문에( 키보드 입력값 유무)
+5. FastAPI는 왜 빠른가. 
+-&gt; 이 이후에는 성준님의 강의를 기대해봅시다.
+2 PRD 의견 공유
+진희 - 시연 화면하고, PRD 공개, 탭으로 따로 했을 경우, 막아놓는 제약 공유
+혜현 - 페르소나 구성 (각 지원자 /담당자의 역할을 정함) 이후 작업 빠르게 진행하고, 안되면 윈도우로 하게끔 진행. 작업속도를 높이는 중.
+지웅(성준) - 기능들을 한번에 다 정리를 함. 
+                 - 면접진행률 - 면접을 봤을 때 필요없는 가능이라고 봄. 
+                 - 발표에 관한 부분. - 개인의 것을 발표했을 때, 문제가 생기지 않을까?- 여기서 나온 질문이긴한데, 일단 궁금증으로 시작
+                 - 예외상황에 대한 질문- 지원자를 중심포인트로 만들어졌음.
+                 - 인수기준=완성기준
+                 - 대체적으로 작성된 이전 사람들 거 기반으로 PRD 구성
+자동로그아웃 세션 = 길게 해야한다 vs 짧게 해야한다.
+10분/1시간/연장하기
+테스트 해보면서 정하기로.
+소현 - 면접 종료 최대 2회로 진행
+        - 프로그램은 크웬위주로 진행(맞는지 체크함)
+        - 하이퍼파라미터로 크웬의 추론 설정 체크(temperature=0.6~0.7 추천)
+TRD에서 하이퍼파라미터 수정예정.
+TRD에서 이 모델을 쓰는 이유를 확실히 명시 승인하는 느낌.
+깃허브에 대한 내용.
+- 팀이 만들었을 때,
+- 가장잘한 사람 한명 껄 공통으로 사용하는지
+- 여러명껄 한번에 넣는지.
+- 하나로 합칠지.
+단체로 다시 작성? 근데 맥으로 사용하는 건 어떻게? 혼자서 함?
+선생님의 답변
+- 팀으로 했을 때, 역할분담이 중요함.
+- 사실상 개발환경 자체가 중요하지 않음(좀더 해설하면, 맥이든 윈도우든 중요한 건 아닐꺼)
+- 가장 잘한 사람꺼 토대로 하면 되지 않느냐.
+- 어떻게 평가할건지에 관한 논의
+- 1인 1프로젝트에 대한 취지설명(팀의 비중차이에 대한 갈등, 개인이 해야 취업이 가능하다.)&gt;&gt; 이에 대한 역할분담.
+- 조별로 진행했을 때, 협업 , 역할분담의 부분만 잘 이뤄지면 상관없음.
+클로드가 일하는 환경 똑같이 만들고, 공유했을 때, 같은 결과인가? = 잘했다면 그럴 수 있지만 그렇게 되기가 힘들다.
+커뮤니케이션에 대한 중요성 다시한번 강조.
+서류작업 - 공통점을 AI 활용해서 만들고, 개인 PRD에서의 특징을 개인이 말해서 해보는건 어떤지에 대한 내용.
+PRD 새로 만들자는 의견. 공통점을 합쳐서 해보자는 의견.</t>
+  </si>
+  <si>
+    <t>PRD 내일까지 확실히 노선정하고 작성하기.</t>
+  </si>
+  <si>
+    <t>내일까지PRD 정리</t>
+  </si>
+  <si>
+    <t>PRD 정리하기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다들 많이 힘들겠지만 내일 PRD 와 일정관리(문서담당)에서 잘 논의해봅시다. </t>
+  </si>
+  <si>
     <t xml:space="preserve">플로우 차트 공유, 역할분담 회의 </t>
   </si>
   <si>
-    <t>2026.10.22 10:10~ 11:10</t>
-  </si>
-  <si>
-    <t>사전 회의</t>
-  </si>
-  <si>
-    <t>참석자</t>
-  </si>
-  <si>
-    <t>지웅, 성준, 진희, 소현, 혜현</t>
-  </si>
-  <si>
-    <t>2026-10-20 17:00~ 18:30</t>
-  </si>
-  <si>
-    <t>작성자</t>
-  </si>
-  <si>
     <t>플로우 차트 공유</t>
   </si>
   <si>
-    <t>진희</t>
-  </si>
-  <si>
-    <t>회의목적</t>
-  </si>
-  <si>
     <t>2026.10.21 15:00~ 17:00</t>
   </si>
   <si>
-    <t>역할, 서류작업 어떻게 진행을 해야할지에 대한 논의</t>
-  </si>
-  <si>
-    <t>요약</t>
-  </si>
-  <si>
-    <t>오늘 오후에 플로우차트 작성 후, 추후 이어지는 논의 진행하기로</t>
-  </si>
-  <si>
-    <t>관리자페이지 기능 과정 마무리 및 추후 방향성 논의</t>
-  </si>
-  <si>
-    <t>주요 내용</t>
-  </si>
-  <si>
     <t>지웅</t>
   </si>
   <si>
-    <t>관리자 페이지에서 필요한 기능과 방향성을 체크, 계획 구체화</t>
-  </si>
-  <si>
     <t>플로우차트가 어떻게 흘러가는지 서로 공유 및 역할분담</t>
   </si>
   <si>
     <t>작성한 플로우차트 공유, 역할 구체화</t>
-  </si>
-  <si>
-    <t>1. 역할 분담에 관한 의견 나눔.
-- DB서버  / llm(AI) / 프론트 으로 역할을 나누려고 했음
-- 시나리오 별로 하면 어떤가?(관리자페이지, 로그인 페이지, 등등)
-- 아키텍처, 문서 작성 후에 진행하면 어떨까? 모두가 찬성. 바로 역할을 정하기엔 아직 시기상조라 생각. 
-- 이후 자연스럽게 문서 작성
-2. 문서작성 관련
-- PRD, 화면정의서, TRD 순서로 나와야 정상적
-- 요새는 순서 상관없이 나오지 않느냐는의견도 있음. 
-- 먼저 각자 생각하는 모델, 프론트에서 어떻게 쓸건지 &lt;넥스트JS, 리엑트&gt; 파이썬, fast API는 확정.
-- LLM 온프리미스 방식으로 할 때 어떤 모델로 쓸 건지 체크
-  →근데 이게 처음부터 정해버리면 돌이킬 수 없는 문제가 발생할 듯..?
-  →일단 여러개를 한번 선상에서 두고, 최선을 골라보자라는 의견이 지배적
-- ★문서대장(Document Register- boss아님)☆
-&gt;&gt; 함수목록 , API명세서(개인별 작성도 체크하기), 플로우차트, TRD,PRD,화면정의서
-&gt;&gt; 이름, 기능, 등등 작성을 해두면 좋을 것.
-&gt;&gt; 추후에 디테일한 내용은 추가예정
-3. 일정 체크. 
-1주차(26~30)- 기본프로그램이 만들어질 정도
-2주차(11/2~ 6)- 프로그램 세부조정(지연시간 단축, 기술적퀄리티 증가&gt;&gt; 소위 튜닝)
-3주차(11/9~13)- 통합테스트
-4주차(16~20)- 추후 서류 작성
-4. 특이사항,
-- 코테 넣기로(총점에 포함하되, 별도의 점수로 체크.)
-- 2차회의는 2시에 진행
-- 개인공부도 진행은 선택</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -185,6 +374,72 @@
 4) 이력서 점수 
 - 이력수 점수를 넣어야 하냐는 의견, 넣는걸로 진행을 하기로 했고 추후에 팀원 회의를 통한 변경 가능성 존재
 </t>
+  </si>
+  <si>
+    <t>PRD 각자 생성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26일 (월) PRD, TRD 1차 생성 </t>
+  </si>
+  <si>
+    <t>임베딩 모델이 어디에 쓰이는지에 대한 구체적인 사용처에 대한 모호함.</t>
+  </si>
+  <si>
+    <t>TRD, PRD, 기타 문서 확인</t>
+  </si>
+  <si>
+    <t>기능관련 회의</t>
+  </si>
+  <si>
+    <t>서류작업 회의</t>
+  </si>
+  <si>
+    <t>사전 회의</t>
+  </si>
+  <si>
+    <t>2026.10.22 10:10~ 11:10</t>
+  </si>
+  <si>
+    <t>2026-10-20 17:00~ 18:30</t>
+  </si>
+  <si>
+    <t>역할, 서류작업 어떻게 진행을 해야할지에 대한 논의</t>
+  </si>
+  <si>
+    <t>관리자페이지 기능 과정 마무리 및 추후 방향성 논의</t>
+  </si>
+  <si>
+    <t>오늘 오후에 플로우차트 작성 후, 추후 이어지는 논의 진행하기로</t>
+  </si>
+  <si>
+    <t>관리자 페이지에서 필요한 기능과 방향성을 체크, 계획 구체화</t>
+  </si>
+  <si>
+    <t>1. 역할 분담에 관한 의견 나눔.
+- DB서버  / llm(AI) / 프론트 으로 역할을 나누려고 했음
+- 시나리오 별로 하면 어떤가?(관리자페이지, 로그인 페이지, 등등)
+- 아키텍처, 문서 작성 후에 진행하면 어떨까? 모두가 찬성. 바로 역할을 정하기엔 아직 시기상조라 생각. 
+- 이후 자연스럽게 문서 작성
+2. 문서작성 관련
+- PRD, 화면정의서, TRD 순서로 나와야 정상적
+- 요새는 순서 상관없이 나오지 않느냐는의견도 있음. 
+- 먼저 각자 생각하는 모델, 프론트에서 어떻게 쓸건지 &lt;넥스트JS, 리엑트&gt; 파이썬, fast API는 확정.
+- LLM 온프리미스 방식으로 할 때 어떤 모델로 쓸 건지 체크
+  →근데 이게 처음부터 정해버리면 돌이킬 수 없는 문제가 발생할 듯..?
+  →일단 여러개를 한번 선상에서 두고, 최선을 골라보자라는 의견이 지배적
+- ★문서대장(Document Register- boss아님)☆
+&gt;&gt; 함수목록 , API명세서(개인별 작성도 체크하기), 플로우차트, TRD,PRD,화면정의서
+&gt;&gt; 이름, 기능, 등등 작성을 해두면 좋을 것.
+&gt;&gt; 추후에 디테일한 내용은 추가예정
+3. 일정 체크. 
+1주차(26~30)- 기본프로그램이 만들어질 정도
+2주차(11/2~ 6)- 프로그램 세부조정(지연시간 단축, 기술적퀄리티 증가&gt;&gt; 소위 튜닝)
+3주차(11/9~13)- 통합테스트
+4주차(16~20)- 추후 서류 작성
+4. 특이사항,
+- 코테 넣기로(총점에 포함하되, 별도의 점수로 체크.)
+- 2차회의는 2시에 진행
+- 개인공부도 진행은 선택</t>
   </si>
   <si>
     <t xml:space="preserve">1. 관리자 페이지에 대한 마무리 기능 상세
@@ -240,49 +495,15 @@
 7. 그외 공유사항은 카톡으로 진행하기. </t>
   </si>
   <si>
-    <t>앞으로 해야할 일</t>
-  </si>
-  <si>
     <t>10월 21일까지 팀장님이 올려주신 기능표 확인하기, TRDPRD 작성하기, 그외에 필요할만한 서류 확인하기.</t>
   </si>
   <si>
-    <t>PRD 각자 생성</t>
-  </si>
-  <si>
-    <t>일정 데드라인</t>
-  </si>
-  <si>
     <t>21일 서류작성</t>
   </si>
   <si>
-    <t xml:space="preserve">26일 (월) PRD, TRD 1차 생성 </t>
-  </si>
-  <si>
-    <t>아직 해소되지 
- 않은 사항</t>
-  </si>
-  <si>
-    <t>임베딩 모델이 어디에 쓰이는지에 대한 구체적인 사용처에 대한 모호함.</t>
-  </si>
-  <si>
     <t xml:space="preserve">PRD TRD작성에 대한 세부적인 부분, 꼬리질문에 관한 논의 </t>
   </si>
   <si>
-    <t>노트</t>
-  </si>
-  <si>
-    <t>팀장님 코멘트</t>
-  </si>
-  <si>
-    <t>2026-10-16 17:30~ 18:30</t>
-  </si>
-  <si>
-    <t>지원자 페이지 기능들을 어떻게 구현하는지에 대한 회의 / 관리자 페이지 작성하기</t>
-  </si>
-  <si>
-    <t>각 페이지 별 기능들과 우선순위(중요도)를 논의</t>
-  </si>
-  <si>
     <t>2026-10-19 17:30~ 18:30</t>
   </si>
   <si>
@@ -290,45 +511,6 @@
   </si>
   <si>
     <t>성준</t>
-  </si>
-  <si>
-    <t>0. 로그인화면이 과연 첫 화면이여야 하는가?
-먼저 공고페이지를 보여주고, 로그인 화면을 선택해서 이동할 수 있게끔 진행하기.
-1. 요구사항 기능정의 표 살펴보기.
-2. 지원자 페이지에 대한 마무리 논의
-(1) 면접완료 안내 페이지 
-- 홈으로 (high) →처음으로 돌아갈 수 있게끔 진행
-- 결과보기(high) →결과리포트 확인하는 버튼 
-- 리포팅 준비중입니다. (high) → 결과보기 활성화되기전 버튼, 나중에 결과보기로 진행하기.
-(2) AI 피드백 페이지
-**방식- 평가항목을 통해서 어떤 기능이 필요한지 가늠하고 체크하기. 중요도는 일단 따로 체크하지 않음.
-☆평가 항목
-질문별 평가(+개념이해도) - 각 질문에 대한 평가 내용. STT된 답변 평가분석 시스템
-논리성- 일관성, 답변의 구체성, 설명의 마무리
-전달력- 말의 속도, 뚜렷함, 음성의 높낮이.
-표현및태도(참여도)- 적극성, 부정적인 단어. 답변시간.
-전문성- 인재상과의 연계 / 회사가치와 맞는지 / 파트에 대한 이해도
-총평- 전체적인 평가 관련된 이야기.  
-총점- 점수 체크하기.
-우선순위 피드백- (좋았던점&lt;강점&gt; -1,2,3순위, 개선점&lt;단점&gt; - 1,2,3순위.)
-이를 위해서 넣어야 하는 기능
-- 시선 트레킹→ 적극성 / 태도와 관련된 부분.
-- 목소리에 대한 높낮이 체크  뚜렷함 등 분석 하는 기능→ 전달력, 참여도
-- STT→ 대화내용을 텍스트로 진행.
-- 감정분석 → 표현및 태도 
-- 답과의 연관성/일관성 분석 →  단어간 벡터 분석
-- 그외 텍스트 분석
-- 답변시간 / 총면접시간
-- AI 평가도구- 텍스트를 통해서 점수를 체크하고 평가하는 시스템.
-3.관리자 페이지 어떤 장면 /기능을 넣을지
-- 로그인 페이지(high)
-- 대시보드(high)
-- 일정관리(high)
-- 면접 질문관리(high)
-- 공고 관리(high)
-- 문의 쪽지(medium)
-4,추후 기능에 대한 이야기
-- UI UX에 관한 이야기.</t>
   </si>
   <si>
     <t>관리자페이지 기능 구성 마무리</t>
@@ -398,19 +580,10 @@
 - 상세 항목: 이력서, 평가 리포트, 항목별 점수, 합격 여부, 질문별 답변, 관리자 메모, 개인 정보(?).</t>
   </si>
   <si>
-    <t>각자 관리자 페이지 어떻게 구성해야할지 고민하기.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">관리자페이지 기능 구성 과제(다음주월요일까지) PRDTRD 다음주 수요일까지 </t>
-  </si>
-  <si>
     <t>화면정의서 작성</t>
   </si>
   <si>
     <t>PRD&amp;TRD 작성 10/21(수)까지</t>
-  </si>
-  <si>
-    <t>전문성에 대한 내용들 체크</t>
   </si>
   <si>
     <t>■ 미결 사항
@@ -419,13 +592,70 @@
 - 일정 관리, 면접 질문(가중치) 화면의 세부 기능</t>
   </si>
   <si>
+    <t>날씨가 많이 추워졌습니다 모두 몸관리 잘하시고 아프시지 마세용 ㅠㅠ</t>
+  </si>
+  <si>
+    <t>2026-10-16 17:30~ 18:30</t>
+  </si>
+  <si>
+    <t>지원자 페이지 기능들을 어떻게 구현하는지에 대한 회의 / 관리자 페이지 작성하기</t>
+  </si>
+  <si>
+    <t>각 페이지 별 기능들과 우선순위(중요도)를 논의</t>
+  </si>
+  <si>
+    <t>0. 로그인화면이 과연 첫 화면이여야 하는가?
+먼저 공고페이지를 보여주고, 로그인 화면을 선택해서 이동할 수 있게끔 진행하기.
+1. 요구사항 기능정의 표 살펴보기.
+2. 지원자 페이지에 대한 마무리 논의
+(1) 면접완료 안내 페이지 
+- 홈으로 (high) →처음으로 돌아갈 수 있게끔 진행
+- 결과보기(high) →결과리포트 확인하는 버튼 
+- 리포팅 준비중입니다. (high) → 결과보기 활성화되기전 버튼, 나중에 결과보기로 진행하기.
+(2) AI 피드백 페이지
+**방식- 평가항목을 통해서 어떤 기능이 필요한지 가늠하고 체크하기. 중요도는 일단 따로 체크하지 않음.
+☆평가 항목
+질문별 평가(+개념이해도) - 각 질문에 대한 평가 내용. STT된 답변 평가분석 시스템
+논리성- 일관성, 답변의 구체성, 설명의 마무리
+전달력- 말의 속도, 뚜렷함, 음성의 높낮이.
+표현및태도(참여도)- 적극성, 부정적인 단어. 답변시간.
+전문성- 인재상과의 연계 / 회사가치와 맞는지 / 파트에 대한 이해도
+총평- 전체적인 평가 관련된 이야기.  
+총점- 점수 체크하기.
+우선순위 피드백- (좋았던점&lt;강점&gt; -1,2,3순위, 개선점&lt;단점&gt; - 1,2,3순위.)
+이를 위해서 넣어야 하는 기능
+- 시선 트레킹→ 적극성 / 태도와 관련된 부분.
+- 목소리에 대한 높낮이 체크  뚜렷함 등 분석 하는 기능→ 전달력, 참여도
+- STT→ 대화내용을 텍스트로 진행.
+- 감정분석 → 표현및 태도 
+- 답과의 연관성/일관성 분석 →  단어간 벡터 분석
+- 그외 텍스트 분석
+- 답변시간 / 총면접시간
+- AI 평가도구- 텍스트를 통해서 점수를 체크하고 평가하는 시스템.
+3.관리자 페이지 어떤 장면 /기능을 넣을지
+- 로그인 페이지(high)
+- 대시보드(high)
+- 일정관리(high)
+- 면접 질문관리(high)
+- 공고 관리(high)
+- 문의 쪽지(medium)
+4,추후 기능에 대한 이야기
+- UI UX에 관한 이야기.</t>
+  </si>
+  <si>
+    <t>각자 관리자 페이지 어떻게 구성해야할지 고민하기.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">관리자페이지 기능 구성 과제(다음주월요일까지) PRDTRD 다음주 수요일까지 </t>
+  </si>
+  <si>
     <t>2026-10-15 17:30~ 18:30</t>
   </si>
   <si>
+    <t>전문성에 대한 내용들 체크</t>
+  </si>
+  <si>
     <t>모두 푹 쉬시고 차주 화이팅... 그리고 기능표는 회의록 기준으로 업데이트를 하지만 혹시나 수정할 부분 있으면 이야기해주세요</t>
-  </si>
-  <si>
-    <t>날씨가 많이 추워졌습니다 모두 몸관리 잘하시고 아프시지 마세용 ㅠㅠ</t>
   </si>
   <si>
     <t>이진희</t>
@@ -490,6 +720,9 @@
 결정되면 자신들이 UX/UI를 제작해서 보여주면 좋을거 같단 생각&gt;&gt; 해당 부분은 금요일에 검토</t>
   </si>
   <si>
+    <t>자세한 것은 공유파일 참고</t>
+  </si>
+  <si>
     <t>관리자페이지 기능 / 지원자페이지 기능 마무리 / PRDTRD</t>
   </si>
   <si>
@@ -502,13 +735,10 @@
     <t>진헤라 죄송합니다.</t>
   </si>
   <si>
+    <t>2026-10-14 17:00~ 18:28</t>
+  </si>
+  <si>
     <t>오늘 다들 고생하셨습니다, 기능 정리 표는 구글드라이브 초안/정리 자료 폴더에 넣어놓겠습니다.</t>
-  </si>
-  <si>
-    <t>자세한 것은 공유파일 참고</t>
-  </si>
-  <si>
-    <t>2026-10-14 17:00~ 18:28</t>
   </si>
   <si>
     <t>면접 절차에 대한 전체적인 흐름을 팀원들이 파악/공유하고, 각 페이지에 어떤 기능을 넣을지에 대한 논의</t>
@@ -589,9 +819,6 @@
     <t>실질적으로 이 기능을 넣는게 유의미한가에 대한 논의를 많이함.</t>
   </si>
   <si>
-    <t>시장조사 및 개요 회의</t>
-  </si>
-  <si>
     <t>0. 와이어프레임 공유(지웅/ 성준)
 1. 명칭 통일
 관리자 / 담당자 / 지원자
@@ -621,31 +848,34 @@
 지원자가 선택? 사실이게 의미가 있는 것인가.</t>
   </si>
   <si>
+    <t>PRD/TRD 작성(다음주 수요일까지) / 기능 관련 회의 종료 (금요일까지)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기능회의 계속 이어서 진행하기. </t>
+  </si>
+  <si>
+    <t>실질적으로 제대로 효용성이 있는 면접이 될 수 있게끔 하는 것. 지원자 / 담당자가 만족을 할 수 있는 '기본'기능을 구현하고 추가 기능을 통해서 차별성을 높이는 것이 중요.</t>
+  </si>
+  <si>
+    <t>혹시라도 틀리거나 곡해된 부분이나, 이상한 부분 있으면 꼭 말씀해주세요.</t>
+  </si>
+  <si>
+    <t>팀장님 코멘트 올려주시면 감사합니다.(사실 이걸로 보시는지 체크하고있어요.)</t>
+  </si>
+  <si>
+    <t>시장조사 및 개요 회의</t>
+  </si>
+  <si>
     <t>시작 설계 회의</t>
   </si>
   <si>
     <t>2026.10.08  17:30~18:33</t>
   </si>
   <si>
-    <t>PRD/TRD 작성(다음주 수요일까지) / 기능 관련 회의 종료 (금요일까지)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기능회의 계속 이어서 진행하기. </t>
-  </si>
-  <si>
     <t xml:space="preserve">시장조사 / 개요 </t>
   </si>
   <si>
     <t>PRD / TRD만들기 전 회의</t>
-  </si>
-  <si>
-    <t>실질적으로 제대로 효용성이 있는 면접이 될 수 있게끔 하는 것. 지원자 / 담당자가 만족을 할 수 있는 '기본'기능을 구현하고 추가 기능을 통해서 차별성을 높이는 것이 중요.</t>
-  </si>
-  <si>
-    <t>혹시라도 틀리거나 곡해된 부분이나, 이상한 부분 있으면 꼭 말씀해주세요.</t>
-  </si>
-  <si>
-    <t>팀장님 코멘트 올려주시면 감사합니다.(사실 이걸로 보시는지 체크하고있어요.)</t>
   </si>
   <si>
     <t>시장조사 관련 느낀점 말하기-성준, 지웅
@@ -685,10 +915,10 @@
     <t>10월 16일까지 PRD TRD작성(아직 미정)</t>
   </si>
   <si>
+    <t>시장조사 회의</t>
+  </si>
+  <si>
     <t>모의면접 / 실전면접</t>
-  </si>
-  <si>
-    <t>시장조사 회의</t>
   </si>
   <si>
     <t>조사후 결과보고</t>
@@ -745,6 +975,9 @@
   </si>
   <si>
     <t>진행 시 역할 분담에 관한 내용과 파일 및 일정관리에 대한 내용</t>
+  </si>
+  <si>
+    <t>AI 모의면접 실제로 해보기</t>
   </si>
   <si>
     <t xml:space="preserve">안건 1. 
@@ -781,34 +1014,31 @@
 </t>
   </si>
   <si>
+    <t>이후 행동에 대한 설계</t>
+  </si>
+  <si>
+    <t>2026.10.01 17:30~ 18:30</t>
+  </si>
+  <si>
+    <t>지웅, 소현, 진희, 혜현, 성준</t>
+  </si>
+  <si>
     <t>시장조사, 엑셀로 정리하기, 결과물에 대한 논의</t>
   </si>
   <si>
     <t>시장조사(~10/5)</t>
   </si>
   <si>
+    <t>AI 모의면접 조사 기획</t>
+  </si>
+  <si>
+    <t>어떤 회사의 AI모의면접을 할지 고민해보고 결정하기</t>
+  </si>
+  <si>
     <t>프로젝트명, 역할분담</t>
   </si>
   <si>
     <t>냉무, 연휴 잘보내시길</t>
-  </si>
-  <si>
-    <t>AI 모의면접 실제로 해보기</t>
-  </si>
-  <si>
-    <t>이후 행동에 대한 설계</t>
-  </si>
-  <si>
-    <t>2026.10.01 17:30~ 18:30</t>
-  </si>
-  <si>
-    <t>지웅, 소현, 진희, 혜현, 성준</t>
-  </si>
-  <si>
-    <t>AI 모의면접 조사 기획</t>
-  </si>
-  <si>
-    <t>어떤 회사의 AI모의면접을 할지 고민해보고 결정하기</t>
   </si>
   <si>
     <t>1. 각자 사람in사이트에 있는 모의면접은 진행해보기(예외 : 소현은 외국 사이트를 다루고 있기 때문에, 거기에 집중)
@@ -1014,7 +1244,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1044,6 +1274,9 @@
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1063,14 +1296,308 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6705600" cy="5629275"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image14.png" title="이미지"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>4295775</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6743700" cy="4695825"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image6.png" title="이미지"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6286500" cy="3867150"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image26.png" title="이미지"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>2505075</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5819775" cy="3371850"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image21.png" title="이미지"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>295275</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5962650" cy="2419350"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image23.png" title="이미지"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>2781300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5419725" cy="3314700"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image10.png" title="이미지"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6791325" cy="4953000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image25.png" title="이미지"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>3219450</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6753225" cy="4953000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image13.png" title="이미지"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>2581275</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6286500" cy="3095625"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image17.png" title="이미지"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="962025" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image22.png"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1082,7 +1609,7 @@
     <xdr:ext cx="7496175" cy="2400300"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image16.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image8.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1103,11 +1630,11 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1119,7 +1646,7 @@
     <xdr:ext cx="3505200" cy="2190750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image11.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1147,7 +1674,7 @@
     <xdr:ext cx="3895725" cy="2438400"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image22.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image20.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1175,7 +1702,7 @@
     <xdr:ext cx="4029075" cy="2514600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image13.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1203,7 +1730,7 @@
     <xdr:ext cx="314325" cy="200025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image28.png"/>
+        <xdr:cNvPr id="0" name="image27.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1224,7 +1751,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1236,7 +1763,7 @@
     <xdr:ext cx="3333750" cy="3343275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image20.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image9.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1264,7 +1791,7 @@
     <xdr:ext cx="3343275" cy="3343275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image15.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image7.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1292,7 +1819,7 @@
     <xdr:ext cx="2581275" cy="2581275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image17.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image18.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1320,7 +1847,7 @@
     <xdr:ext cx="2743200" cy="1371600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image19.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1348,7 +1875,7 @@
     <xdr:ext cx="2057400" cy="1371600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image8.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image16.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1376,7 +1903,7 @@
     <xdr:ext cx="2190750" cy="1819275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image12.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1398,6 +1925,18 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1409,7 +1948,7 @@
     <xdr:ext cx="1819275" cy="3714750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image19.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image15.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1465,7 +2004,7 @@
     <xdr:ext cx="1819275" cy="3571875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image10.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1493,7 +2032,7 @@
     <xdr:ext cx="3143250" cy="3371850"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image9.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1521,7 +2060,7 @@
     <xdr:ext cx="1743075" cy="4295775"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image11.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image5.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1542,7 +2081,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1554,7 +2093,7 @@
     <xdr:ext cx="6600825" cy="2981325"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image21.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image4.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1575,11 +2114,11 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1591,305 +2130,11 @@
     <xdr:ext cx="6734175" cy="5438775"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image25.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image28.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="6705600" cy="5629275"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image18.png" title="이미지"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>4295775</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="6743700" cy="4695825"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image14.png" title="이미지"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="6286500" cy="3867150"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image12.png" title="이미지"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>2505075</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5819775" cy="3371850"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image23.png" title="이미지"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>295275</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5962650" cy="2419350"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image27.png" title="이미지"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>2781300</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5419725" cy="3314700"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="6791325" cy="4953000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>3219450</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="6753225" cy="4953000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>2581275</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="6286500" cy="3095625"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image7.png" title="이미지"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="962025" cy="552450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image26.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2133,43 +2378,43 @@
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4"/>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4"/>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4"/>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C6" s="4"/>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4"/>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4"/>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6"/>
     </row>
@@ -2179,31 +2424,31 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4"/>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -2267,20 +2512,20 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>83</v>
@@ -2288,42 +2533,42 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -2332,39 +2577,43 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="1"/>
@@ -2411,6 +2660,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="2" max="2" width="13.88"/>
     <col customWidth="1" min="3" max="3" width="95.88"/>
   </cols>
   <sheetData>
@@ -2426,64 +2676,68 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>95</v>
+        <v>53</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="P9" s="13"/>
     </row>
     <row r="10" ht="306.75" customHeight="1">
       <c r="B10" s="7"/>
@@ -2491,41 +2745,43 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="1"/>
@@ -2587,63 +2843,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -2652,41 +2908,43 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="1"/>
@@ -2748,63 +3006,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>118</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -2813,39 +3071,37 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>125</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -2909,64 +3165,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="H2" s="12"/>
+        <v>120</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>118</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -2975,39 +3230,39 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -3071,63 +3326,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -3136,39 +3391,523 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
+        <v>19</v>
+      </c>
+      <c r="C15" s="9"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="H2:N15"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="95.88"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="H1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" ht="439.5" customHeight="1">
+      <c r="B9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" ht="306.75" customHeight="1">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="9"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="H2:N15"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="95.88"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="H1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" ht="439.5" customHeight="1">
+      <c r="B9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" ht="306.75" customHeight="1">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="9"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="H2:N15"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="95.88"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="H1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" ht="439.5" customHeight="1">
+      <c r="B9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" ht="306.75" customHeight="1">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -3232,63 +3971,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -3297,37 +4036,33 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>32</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C11" s="4"/>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>37</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C13" s="4"/>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -3391,63 +4126,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -3456,31 +4191,35 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -3544,63 +4283,66 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>3</v>
+        <v>23</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -3609,39 +4351,41 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="1"/>
@@ -3703,20 +4447,20 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>44</v>
@@ -3724,42 +4468,42 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -3768,41 +4512,39 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>59</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C15" s="9"/>
     </row>
     <row r="16">
       <c r="B16" s="1"/>
@@ -3864,63 +4606,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -3929,41 +4671,33 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>51</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C11" s="4"/>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>52</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C12" s="4"/>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>55</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C13" s="4"/>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>58</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C15" s="9"/>
     </row>
     <row r="16">
       <c r="B16" s="1"/>
@@ -4025,20 +4759,20 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>57</v>
@@ -4046,42 +4780,42 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -4090,43 +4824,39 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C15" s="9"/>
     </row>
     <row r="16">
       <c r="B16" s="1"/>
@@ -4173,7 +4903,6 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="13.88"/>
     <col customWidth="1" min="3" max="3" width="95.88"/>
   </cols>
   <sheetData>
@@ -4189,47 +4918,44 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>70</v>
@@ -4237,20 +4963,19 @@
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="P9" s="12"/>
+        <v>11</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
       <c r="B10" s="7"/>
@@ -4258,39 +4983,37 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>75</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>76</v>
@@ -4356,20 +5079,20 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>77</v>
@@ -4377,23 +5100,23 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>78</v>
@@ -4401,7 +5124,7 @@
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>79</v>
@@ -4409,10 +5132,10 @@
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -4421,42 +5144,40 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>89</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">

--- a/회의록.xlsx
+++ b/회의록.xlsx
@@ -4,23 +4,24 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="회의록 원본" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="20261028" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="20261027" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="20261026" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="20261022 오후" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="20261022오전" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="20261020" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="20261019" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="20261016" sheetId="9" r:id="rId13"/>
-    <sheet state="visible" name="20261015" sheetId="10" r:id="rId14"/>
-    <sheet state="visible" name="20261014" sheetId="11" r:id="rId15"/>
-    <sheet state="visible" name="20261013" sheetId="12" r:id="rId16"/>
-    <sheet state="visible" name="20261008" sheetId="13" r:id="rId17"/>
-    <sheet state="visible" name="20261006" sheetId="14" r:id="rId18"/>
-    <sheet state="visible" name="20261002" sheetId="15" r:id="rId19"/>
-    <sheet state="visible" name="20261001" sheetId="16" r:id="rId20"/>
-    <sheet state="visible" name="20260929" sheetId="17" r:id="rId21"/>
-    <sheet state="visible" name="20260923" sheetId="18" r:id="rId22"/>
+    <sheet state="visible" name="20261030" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="20261028" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="20261027" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="20261026" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="20261022 오후" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="20261022오전" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="20261020" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="20261019" sheetId="9" r:id="rId13"/>
+    <sheet state="visible" name="20261016" sheetId="10" r:id="rId14"/>
+    <sheet state="visible" name="20261015" sheetId="11" r:id="rId15"/>
+    <sheet state="visible" name="20261014" sheetId="12" r:id="rId16"/>
+    <sheet state="visible" name="20261013" sheetId="13" r:id="rId17"/>
+    <sheet state="visible" name="20261008" sheetId="14" r:id="rId18"/>
+    <sheet state="visible" name="20261006" sheetId="15" r:id="rId19"/>
+    <sheet state="visible" name="20261002" sheetId="16" r:id="rId20"/>
+    <sheet state="visible" name="20261001" sheetId="17" r:id="rId21"/>
+    <sheet state="visible" name="20260929" sheetId="18" r:id="rId22"/>
+    <sheet state="visible" name="20260923" sheetId="19" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="181">
   <si>
     <t>참고자료</t>
   </si>
@@ -36,59 +37,154 @@
     <t>회의명</t>
   </si>
   <si>
+    <t>PRD 피드백 및 업무 시간 분배에 대한 회의</t>
+  </si>
+  <si>
+    <t>AI 아키텍처 관련 회의</t>
+  </si>
+  <si>
     <t>회의 유형</t>
   </si>
   <si>
+    <t>문서 작성 회의</t>
+  </si>
+  <si>
+    <t>PRD 관련해서 어떻게 해야할지에 대한 회의</t>
+  </si>
+  <si>
     <t>회의 일시</t>
   </si>
   <si>
-    <t>PRD 피드백 및 업무 시간 분배에 대한 회의</t>
+    <t>2026-10-30 10:10 ~ 10:40</t>
+  </si>
+  <si>
+    <t>[WBS 리뷰 - 선생님 피드백]
+■ 공통
+1. 일정 구조
+- WBS는 날짜 순서대로 시퀀스가 맞아야 한다. 날짜가 왔다 갔다 하면 안 된다.
+- 항목마다 전담자를 정한다. 공통 작업이라도 실질적으로 담당하는 사람을 명시한다. 
+- 작업량이 많으므로 하루하루 여유 있게 가는 방식은 안 된다. 
+- 전담을 정하고 언제까지 무엇을 할지 세부적으로 잡는다.
+2. 개발 환경
+- 개발 환경 세팅이 먼저 돼야 개발을 진행할 수 있다. 세팅이 틀어지면 뒤 일정이 전부 밀린다.
+- 모델 선택은 나중에 해도 되지만 세팅은 먼저 마무리한다. 모델은 나중에 바꿀 수 있다.
+- 도커로 서버 환경을 준비한다. 웹, FastAPI 등 필요한 서버를 Docker Compose로 한 번에 올렸다 내렸다 할 수 있게 구성한다. 메모리 사양도 함께 확인한다.
+- 설명서는 서버와 도커 구성을 다룬다.
+- 세팅에 3일 이상 걸리면 일주일이 날아갈 수 있다. 팀 간 공유를 필수로 하며, 세팅을 잘하는 팀원(찬성 님)이 각 팀을 돌며 같이 본다.
+■ 1팀
+1. 개발 환경 (1.2)
+- 개발 환경 구축 방식이 상세하지 않다. 내일(목요일)까지 1차 완료를 목표로 한다.
+- 개발 환경은 아래 개발 항목이 돌아갈 수 있도록 맞춘다. 필요한 라이브러리(STT, TTS, 면접 진행 등)도 포함한다
+2. AI 모델 PoC
+- 일정이 과하다. 하루에 끝날 분량이 아니며 2~3일이 걸린다.
+- 크게 잡고, 함수 테스트 단위로 세분화해서 진행한다.
+3. 2.2 (공고 연동)
+- 개인이 알아보는 조사 대상이 아니다.
+- 공고 목록, 상세, 연동 부분은 수집 대상이다. 수집해야 모의 면접 시스템에 가상으로 접수하고 진행할 수 있다.
+4. 코딩 테스트 및 부가 기능
+- 코딩 테스트는 필수가 아니라 선택 사항이다.
+- 준비가 안 됐다면 빼는 게 맞다. 준비가 돼 있다면 진행해도 된다. 팀별 사정에 따라 판단한다.
+- 코딩 테스트 에이전시, 화이트보드, 마이페이지는 빼는 방향으로 말씀하셨다. 화이트보드는 제외 의사를 명확히 밝히셨다.
+■ 2팀 - 우리팀 내용
+1. 테스트 계획서 (2.2, 2.3)
+- 테스트 계획서와 테스트 케이스 작성은 2주차 위치수정
+- 작성만 하지 말고 테스트를 실제로 진행하는 것까지 포함한다.
+- 3주차에 테스트만 따로 진행하는 구조는 안 된다. 2주차 작업이 3주차까지 이어진다.
+2. 2주차·3주차 구성
+- 두 주차가 전체적으로 문제가 많다. 다시 수정한다.
+- 두 주차를 맞물리게 조정한다.
+- "백엔드 API 구현 → 테스트", "화면 구현 → 테스트"처럼 기능 단위로 분할한다.
+3. 세부 항목
+- 2.4.4 (AI 기능 연동): 두루뭉술하다. 핵심 항목이므로 세분화한다. 3주차 내용보다 커야 한다.
+- 관리자 기능: 백엔드와 같이 들어가는 항목이다.
+- 순서: 화면 구현과 백엔드 순서가 뒤바뀌어 있다. 수정한다.
+- 용어: "구현 작업"이라는 표현은 맞지 않다. DB 구축은 아키텍처와 개발 환경에 속하는 항목이다.
+- 테스트 용어: "재테스트"는 단위 테스트로 쓴다. "버그 수정"이라는 항목명은 쓰지 않는다.
+- 1주차:  1.11번은 예상 완료일이 1주차에 완료가 돼야한다
+- 개발 기간: 개발이 일주일에 끝날 것 같냐고 물으셨다. 일정을 다시 검토해서 수정한다.
+■ 3팀
+1. 개발 기간 및 검증
+- 6번(코드 작성)과 7번(테스트, 오류 수정)을 묶는다. 개발, 검증, 오류 수정을 한 덩어리로 본다.
+- 6번은 11월 9일 시작, 10일까지로 잡혀 있었으나 11월 17일까지로 늘린다. 발표 자료 작성도 이 기간에 포함한다.
+- 음성 면접, 리포트 구현, 코딩 테스트는 각각 최소 5일이 필요하다. 하루 이틀에 끝나지 않는다.
+- 이 구간은 노란색으로 표시한다. 기간이 줄어들 위험이 있다는 뜻이다.
+2. 항목 분할
+- 음성 면접: 범위가 매우 크다. TTS, STT, 꼬리 질문 등으로 나눈다.
+- 리포트 구현: 나눌 필요가 있다.
+- 등급 엔진 및 공통 기반: MVC 단독 구현은 의미가 적다.</t>
   </si>
   <si>
     <t>참석자</t>
   </si>
   <si>
+    <t>정기회의 + 팀의 방향을 잡아가는 회의</t>
+  </si>
+  <si>
+    <t>지웅, 성준, 진희, 혜현</t>
+  </si>
+  <si>
+    <t>피드백 회의</t>
+  </si>
+  <si>
     <t>작성자</t>
   </si>
   <si>
+    <t>2026-10-27 10:20~ 11:10</t>
+  </si>
+  <si>
+    <t>진희</t>
+  </si>
+  <si>
+    <t>2026-10-28 10:20~11:30, 15:00~16:00</t>
+  </si>
+  <si>
     <t>회의목적</t>
   </si>
   <si>
-    <t>피드백 회의</t>
+    <t>AI 아키텍처 관련 어떻게 진행할지에 대한 회의</t>
+  </si>
+  <si>
+    <t>지웅, 성준, 진희, 소현, 혜현</t>
   </si>
   <si>
     <t>요약</t>
   </si>
   <si>
-    <t>2026-10-28 10:20~11:30, 15:00~16:00</t>
+    <t>AI 아키텍처 문서에 대한 소통 내용 및 이후, 추후 일정에 대한 소통 진행</t>
+  </si>
+  <si>
+    <t>업무에 대한 피드백</t>
   </si>
   <si>
     <t>주요 내용</t>
   </si>
   <si>
-    <t>지웅, 성준, 진희, 소현, 혜현</t>
-  </si>
-  <si>
-    <t>진희</t>
-  </si>
-  <si>
-    <t>업무에 대한 피드백</t>
-  </si>
-  <si>
-    <t>앞으로 해야할 일</t>
-  </si>
-  <si>
-    <t>일정 데드라인</t>
-  </si>
-  <si>
-    <t>아직 해소되지 
- 않은 사항</t>
-  </si>
-  <si>
-    <t>노트</t>
-  </si>
-  <si>
-    <t>팀장님 코멘트</t>
+    <t>지웅,성준,진희,소현,혜현</t>
+  </si>
+  <si>
+    <t>1. AI 아키텍처에 관한 회의
+(1) 모델은 어떻게 사용할건지.
+- 모델은 대체적으로 비슷하게 만들어짐(QWEN, BGE-M3, whisper 등등)
+- 하지만, 모델에 따라서 성능이 바뀌고, 이를 확정을 지을 수 없음.
+- 그래서 모델은 개개인 별로 다르게 진행하기(일단 크게 결정을 짓지 않기로)
+(2) 구조를 짜기.
+파이프라인과, AI의 역할, 어떻게 진행할지에 대한 내용 회의
+(3) 랭체인과 랭그래프 둘중 어떤것? 랭체인만 쓰라고 할 때도 있던데?
+- 랭체인은 단방향이고, 랭그래프는 구조적으로 돌아가지않나? 랭체인이 더 가벼울거같은데.
+- 그냥 랭그래프를 쓰라는게 주 의견.
+- 웬만하면 랭그래프로 처리하는게 좋음.
+(4) 영찬님이 말씀하신 부분에 대한 내용.
+- RAG관련해서 하신말씀이있다던데, 나중에 들어보기로.
+2. 그 이후 행동방향,
+(1) 드디어 구현
+(2) 구현 후, 피드백을 진행하면 될듯.
+3. 디자인 관련해서 샘플이 있으면 좋을거같음.
+(1) 화면정의서대로 구현하라고 보니까. 디자인이 좀 구린 면이 없지않아 있다.
+(2) 좀 세련되게 진행하기 위해서 참고할만한 디자인을 해보자.
+4. 추후 이용 방법 정리
+(1) 성준님이 AI 아키텍처 작성.
+(2) 진희님이 검토 후 다시 패치버전 올림.
+(3) 이후, 성준님 승인 후, 다른 사람들에게 배포. 그리고 작업진행.</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -139,19 +235,68 @@
 이에 대한 대처법도 생각해놓자.</t>
   </si>
   <si>
+    <t>팀의 방향 잡아가기.</t>
+  </si>
+  <si>
+    <t>서류작성의 경우 팀에서 함께 조율하며 담당하기.</t>
+  </si>
+  <si>
+    <t>앞으로 해야할 일</t>
+  </si>
+  <si>
+    <t>일정 데드라인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 진희의 오전 한마디(?)
+- 요약: 팀으로 할건지, 개인으로 할건지 확실히 정하자.
+- 결론 : 팀으로 서류작업을 처리하자.
+- 조건 : 팀이 하는 결론에 대해서 모두가 이의가 없도록.(이미 결론이 난 사항에 대해서는)
+- 조건2 : 진행중에 있는 불만에 대해서는 확실히 이야기해서 해소할 수 있도록.
+- 조건3 : 서류간 문제가 있을 경우 담당자간 확인 후 조율 후 진행(1차 담당자간-&gt; 2차 팀원전체)
+2. 성준의 모두의 것을 합친 PRD
+- 이어서 PRD 담당자(정:소현, 부:지웅)이 진행.
+- 검토 후에 초안을 내고, 팀원들의 검토가 필요.
+- 토큰 분배 필요할듯. 
+=&gt; 문서를 다루는데에는 크게 문제가 없었지만, 실제 구현 단계에서 문제가 됨
+- 그래서 정부 따로 진행하기로 함.
+3. 서류 리스트 및 서류 담당자 진행.
+- 전체적인 책임자. 책임자가 해당 서류에 대한 의견을 남길 수 있도록.
+- 마감일자 지정. 오늘 플로우차트 완성(혜현,진희) , WBS(지웅,진희,혜현)
+- 내일 PRD(소현,지웅), TRD(성준,소현), 화면정의서(진희,혜현)
+4. 이후 팀장회의에 갔음.
+내용 요약: 팀과 개인간의 어떻게 해야할지 방향잡기, 팀별로 어떻게 하기로 결정했는지.
+추가제안: 
+매일 회의에 작성이 완료된 서류를 검토하고(사전에 읽어오기) 문제점들을 체크하고 담당자의 버전업 시키기.
+추가 오후 회의:
+성준&amp;소현 - PRD관련 이야기 도중 중간에 평가기준에 대해서 간단히라도 지원자에게 공개하는 문구에 대한 내용 이야기
+질문에 대한 체크 - 우리가 질문을 만들때 어떻게 만드는지에 대한 재정립- 벡터DB? 질문은행? 이에 대한 방향을 확실히 잡아감.
+꼬리질문에 대한 내용- 어떨때 꼬리질문을 불러오는지에 대한 내용.
+LLM활용에 있어서 질문활용- 괜찮은 질문에 대한 정의 </t>
+  </si>
+  <si>
     <t>10/30(금)        기능정의서, 시나리오 기획서, TRD, 기술 아키텍처, 화면정의서 초안. API 명세서는 1차본</t>
   </si>
   <si>
-    <t>PRD 관련해서 어떻게 해야할지에 대한 회의</t>
+    <t>구현</t>
+  </si>
+  <si>
+    <t>아직 해소되지 
+ 않은 사항</t>
+  </si>
+  <si>
+    <t>팀장님 결정사항 공유</t>
+  </si>
+  <si>
+    <t xml:space="preserve">플로우차트, WBS(오늘까지) PRD,TRD,화면정의서(내일까지) </t>
+  </si>
+  <si>
+    <t>노트</t>
+  </si>
+  <si>
+    <t>팀장님 코멘트</t>
   </si>
   <si>
     <t>PRD 작성 이후 관련 토의</t>
-  </si>
-  <si>
-    <t>정기회의 + 팀의 방향을 잡아가는 회의</t>
-  </si>
-  <si>
-    <t>2026-10-27 10:20~ 11:10</t>
   </si>
   <si>
     <t># AI 채용 플랫폼 PRD 4종 공통점 요약
@@ -190,15 +335,6 @@
 네 PRD는 기업의 채용공고와 지원자 정보를 기반으로 AI 면접 및 코딩테스트를 수행하고, 루브릭 기반 평가 결과를 제공하여 채용 담당자의 최종 의사결정을 지원한다는 공통 목적을 가진다. 다만 세부 운영 정책과 구현 범위는 추가 합의가 필요하다.</t>
   </si>
   <si>
-    <t>지웅,성준,진희,소현,혜현</t>
-  </si>
-  <si>
-    <t>팀의 방향 잡아가기.</t>
-  </si>
-  <si>
-    <t>서류작성의 경우 팀에서 함께 조율하며 담당하기.</t>
-  </si>
-  <si>
     <t>구체적인 기획 회의</t>
   </si>
   <si>
@@ -212,37 +348,13 @@
 성준 RE : ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ</t>
   </si>
   <si>
-    <t xml:space="preserve">1. 진희의 오전 한마디(?)
-- 요약: 팀으로 할건지, 개인으로 할건지 확실히 정하자.
-- 결론 : 팀으로 서류작업을 처리하자.
-- 조건 : 팀이 하는 결론에 대해서 모두가 이의가 없도록.(이미 결론이 난 사항에 대해서는)
-- 조건2 : 진행중에 있는 불만에 대해서는 확실히 이야기해서 해소할 수 있도록.
-- 조건3 : 서류간 문제가 있을 경우 담당자간 확인 후 조율 후 진행(1차 담당자간-&gt; 2차 팀원전체)
-2. 성준의 모두의 것을 합친 PRD
-- 이어서 PRD 담당자(정:소현, 부:지웅)이 진행.
-- 검토 후에 초안을 내고, 팀원들의 검토가 필요.
-- 토큰 분배 필요할듯. 
-=&gt; 문서를 다루는데에는 크게 문제가 없었지만, 실제 구현 단계에서 문제가 됨
-- 그래서 정부 따로 진행하기로 함.
-3. 서류 리스트 및 서류 담당자 진행.
-- 전체적인 책임자. 책임자가 해당 서류에 대한 의견을 남길 수 있도록.
-- 마감일자 지정. 오늘 플로우차트 완성(혜현,진희) , WBS(지웅,진희,혜현)
-- 내일 PRD(소현,지웅), TRD(성준,소현), 화면정의서(진희,혜현)
-4. 이후 팀장회의에 갔음.
-내용 요약: 팀과 개인간의 어떻게 해야할지 방향잡기, 팀별로 어떻게 하기로 결정했는지.
-추가제안: 
-매일 회의에 작성이 완료된 서류를 검토하고(사전에 읽어오기) 문제점들을 체크하고 담당자의 버전업 시키기.
-추가 오후 회의:
-성준&amp;소현 - PRD관련 이야기 도중 중간에 평가기준에 대해서 간단히라도 지원자에게 공개하는 문구에 대한 내용 이야기
-질문에 대한 체크 - 우리가 질문을 만들때 어떻게 만드는지에 대한 재정립- 벡터DB? 질문은행? 이에 대한 방향을 확실히 잡아감.
-꼬리질문에 대한 내용- 어떨때 꼬리질문을 불러오는지에 대한 내용.
-LLM활용에 있어서 질문활용- 괜찮은 질문에 대한 정의 </t>
-  </si>
-  <si>
-    <t>팀장님 결정사항 공유</t>
-  </si>
-  <si>
-    <t xml:space="preserve">플로우차트, WBS(오늘까지) PRD,TRD,화면정의서(내일까지) </t>
+    <t>기능관련 회의</t>
+  </si>
+  <si>
+    <t>사전 회의</t>
+  </si>
+  <si>
+    <t>2026-10-20 17:00~ 18:30</t>
   </si>
   <si>
     <t>1 혜현님의 API 강의
@@ -294,152 +406,19 @@
 PRD 새로 만들자는 의견. 공통점을 합쳐서 해보자는 의견.</t>
   </si>
   <si>
+    <t>관리자페이지 기능 과정 마무리 및 추후 방향성 논의</t>
+  </si>
+  <si>
     <t>PRD 내일까지 확실히 노선정하고 작성하기.</t>
   </si>
   <si>
+    <t>관리자 페이지에서 필요한 기능과 방향성을 체크, 계획 구체화</t>
+  </si>
+  <si>
     <t>내일까지PRD 정리</t>
   </si>
   <si>
     <t>PRD 정리하기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">다들 많이 힘들겠지만 내일 PRD 와 일정관리(문서담당)에서 잘 논의해봅시다. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">플로우 차트 공유, 역할분담 회의 </t>
-  </si>
-  <si>
-    <t>플로우 차트 공유</t>
-  </si>
-  <si>
-    <t>2026.10.21 15:00~ 17:00</t>
-  </si>
-  <si>
-    <t>지웅</t>
-  </si>
-  <si>
-    <t>플로우차트가 어떻게 흘러가는지 서로 공유 및 역할분담</t>
-  </si>
-  <si>
-    <t>작성한 플로우차트 공유, 역할 구체화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-플로우 차트는 공유 드라이브 화면 흐름도에서 확인 가능
-1) 플로우 차트 공유 
--성준
-- 시나리오 별 플로우 차트
-- 면접중 임의로 세션을 이탈시 초기화되는 악용 경고메세지
-- 오어스를 넣을것인가? 오어스가 존재하되 가입을 먼저해야한다
-- 소현 
-- 대시보드 화면에 처음 들어갔을때 통계적인 화면이 보이는 것보다 공고 화면이 먼저 보이는게 중요하다 통계
- 화면은 따로 사이드바 쪽으로 해서 따로 배치
-- 그렇게 됐을때 보여지는 화면이 다르기때문에 엔드포인트가 다르다는 우려, 하지만 코드만 달라지기때문에
- 엔드포인트에 관해서는 괜찮다는 의견
-- AI예상 스코어 제거 
-- 지웅
-- 전체적인 플로우 차트는 기능적인 부분에서 따라가는 방향, 질문을 DB에 넣고 AI 뽑아서 생성하는 방향으로 
- 플로우 차트 진행
-- 코딩테스트 부분에서 monaco editor를 사용하고 judge0를 사용하는 방식을 채택해서 설명
-- 완료후 어느 화면이 들어오는지에 대한 질문과 메인페이지로 돌아간다는 답변
-- 진희
-- 다양한 플로우 차트 ( 전체플로우, 질문생성 플로우, 챙둉결과 리포트, 코테관련 ) 공유
-- 질문생성 플로우.png에서 관리자 입력질문, DB에 존재하는 질문은행 선택, LLM이 랜덤으로 생성하는 3가지 방식
- 보여줌 
- └ 선생님께서 관리자가 수동으로 입력할 질문이 필요한가? AI를 사용하는데 굳이 수동으로 할 필요가 있는지에 
- 대한 피드백
-- 코딩테스트에 관한 플로우, 함정설계 플로우 부분에서 정보 제한, 오류 유도, 모호한 요구로 함정 설계를 해보는
- 방안도 어떠냐 라는 제안
--혜현
-- 답변을 완벽하게 했을때 꼬리질문이 나오지 않고 다음 단계로 진행 
-- 지원자 상세 평가 보기 부분에서 음성 타임라인 하이라이트 플레이어 우수/감점 구간 바로 듣기 기능을 추가해서
- 플로우 차트를 만들었고 좋다는 반응
----------------------------------------------------
-2) API 관련 부분
-LLM을 로컬로 다운받아 사용을 할것인가 외부 API를 사용해서 사용할것인가
-- 로컬로 확정
-2.1) 모델 
-LLM모델로는 Qwen, DeepSeek가 존재하며 현재 정해진 모델은 Qwen을 사용할 예정
-Embedding 모델로는 Qwen3 임베딩 모델을 사용할 예정
-TTS - Whisper Large-V3 Turbo 사용할 예정 
-----------------------------------------------------
-3) 역할분담
-- 1차 확정 -&gt; 추후 변경될 가능성이 있음
-└ 질문 분석(이력서/꼬리질문)
-└ 음성 영상
-└ 평가(리포트)
-└ 코딩테스트 
-2 / 1 / 1 / 1 로 나눠서 하자는 의견
-----------------------------------------------------
-4) 이력서 점수 
-- 이력수 점수를 넣어야 하냐는 의견, 넣는걸로 진행을 하기로 했고 추후에 팀원 회의를 통한 변경 가능성 존재
-</t>
-  </si>
-  <si>
-    <t>PRD 각자 생성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26일 (월) PRD, TRD 1차 생성 </t>
-  </si>
-  <si>
-    <t>임베딩 모델이 어디에 쓰이는지에 대한 구체적인 사용처에 대한 모호함.</t>
-  </si>
-  <si>
-    <t>TRD, PRD, 기타 문서 확인</t>
-  </si>
-  <si>
-    <t>기능관련 회의</t>
-  </si>
-  <si>
-    <t>서류작업 회의</t>
-  </si>
-  <si>
-    <t>사전 회의</t>
-  </si>
-  <si>
-    <t>2026.10.22 10:10~ 11:10</t>
-  </si>
-  <si>
-    <t>2026-10-20 17:00~ 18:30</t>
-  </si>
-  <si>
-    <t>역할, 서류작업 어떻게 진행을 해야할지에 대한 논의</t>
-  </si>
-  <si>
-    <t>관리자페이지 기능 과정 마무리 및 추후 방향성 논의</t>
-  </si>
-  <si>
-    <t>오늘 오후에 플로우차트 작성 후, 추후 이어지는 논의 진행하기로</t>
-  </si>
-  <si>
-    <t>관리자 페이지에서 필요한 기능과 방향성을 체크, 계획 구체화</t>
-  </si>
-  <si>
-    <t>1. 역할 분담에 관한 의견 나눔.
-- DB서버  / llm(AI) / 프론트 으로 역할을 나누려고 했음
-- 시나리오 별로 하면 어떤가?(관리자페이지, 로그인 페이지, 등등)
-- 아키텍처, 문서 작성 후에 진행하면 어떨까? 모두가 찬성. 바로 역할을 정하기엔 아직 시기상조라 생각. 
-- 이후 자연스럽게 문서 작성
-2. 문서작성 관련
-- PRD, 화면정의서, TRD 순서로 나와야 정상적
-- 요새는 순서 상관없이 나오지 않느냐는의견도 있음. 
-- 먼저 각자 생각하는 모델, 프론트에서 어떻게 쓸건지 &lt;넥스트JS, 리엑트&gt; 파이썬, fast API는 확정.
-- LLM 온프리미스 방식으로 할 때 어떤 모델로 쓸 건지 체크
-  →근데 이게 처음부터 정해버리면 돌이킬 수 없는 문제가 발생할 듯..?
-  →일단 여러개를 한번 선상에서 두고, 최선을 골라보자라는 의견이 지배적
-- ★문서대장(Document Register- boss아님)☆
-&gt;&gt; 함수목록 , API명세서(개인별 작성도 체크하기), 플로우차트, TRD,PRD,화면정의서
-&gt;&gt; 이름, 기능, 등등 작성을 해두면 좋을 것.
-&gt;&gt; 추후에 디테일한 내용은 추가예정
-3. 일정 체크. 
-1주차(26~30)- 기본프로그램이 만들어질 정도
-2주차(11/2~ 6)- 프로그램 세부조정(지연시간 단축, 기술적퀄리티 증가&gt;&gt; 소위 튜닝)
-3주차(11/9~13)- 통합테스트
-4주차(16~20)- 추후 서류 작성
-4. 특이사항,
-- 코테 넣기로(총점에 포함하되, 별도의 점수로 체크.)
-- 2차회의는 2시에 진행
-- 개인공부도 진행은 선택</t>
   </si>
   <si>
     <t xml:space="preserve">1. 관리자 페이지에 대한 마무리 기능 상세
@@ -495,15 +474,187 @@
 7. 그외 공유사항은 카톡으로 진행하기. </t>
   </si>
   <si>
+    <t xml:space="preserve">다들 많이 힘들겠지만 내일 PRD 와 일정관리(문서담당)에서 잘 논의해봅시다. </t>
+  </si>
+  <si>
+    <t>TRD, PRD, 기타 문서 확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">플로우 차트 공유, 역할분담 회의 </t>
+  </si>
+  <si>
+    <t>서류작업 회의</t>
+  </si>
+  <si>
     <t>10월 21일까지 팀장님이 올려주신 기능표 확인하기, TRDPRD 작성하기, 그외에 필요할만한 서류 확인하기.</t>
   </si>
   <si>
     <t>21일 서류작성</t>
   </si>
   <si>
+    <t>플로우 차트 공유</t>
+  </si>
+  <si>
+    <t>2026.10.22 10:10~ 11:10</t>
+  </si>
+  <si>
+    <t>2026.10.21 15:00~ 17:00</t>
+  </si>
+  <si>
+    <t>지웅</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRD TRD작성에 대한 세부적인 부분, 꼬리질문에 관한 논의 </t>
   </si>
   <si>
+    <t>역할, 서류작업 어떻게 진행을 해야할지에 대한 논의</t>
+  </si>
+  <si>
+    <t>플로우차트가 어떻게 흘러가는지 서로 공유 및 역할분담</t>
+  </si>
+  <si>
+    <t>오늘 오후에 플로우차트 작성 후, 추후 이어지는 논의 진행하기로</t>
+  </si>
+  <si>
+    <t>작성한 플로우차트 공유, 역할 구체화</t>
+  </si>
+  <si>
+    <t>1. 역할 분담에 관한 의견 나눔.
+- DB서버  / llm(AI) / 프론트 으로 역할을 나누려고 했음
+- 시나리오 별로 하면 어떤가?(관리자페이지, 로그인 페이지, 등등)
+- 아키텍처, 문서 작성 후에 진행하면 어떨까? 모두가 찬성. 바로 역할을 정하기엔 아직 시기상조라 생각. 
+- 이후 자연스럽게 문서 작성
+2. 문서작성 관련
+- PRD, 화면정의서, TRD 순서로 나와야 정상적
+- 요새는 순서 상관없이 나오지 않느냐는의견도 있음. 
+- 먼저 각자 생각하는 모델, 프론트에서 어떻게 쓸건지 &lt;넥스트JS, 리엑트&gt; 파이썬, fast API는 확정.
+- LLM 온프리미스 방식으로 할 때 어떤 모델로 쓸 건지 체크
+  →근데 이게 처음부터 정해버리면 돌이킬 수 없는 문제가 발생할 듯..?
+  →일단 여러개를 한번 선상에서 두고, 최선을 골라보자라는 의견이 지배적
+- ★문서대장(Document Register- boss아님)☆
+&gt;&gt; 함수목록 , API명세서(개인별 작성도 체크하기), 플로우차트, TRD,PRD,화면정의서
+&gt;&gt; 이름, 기능, 등등 작성을 해두면 좋을 것.
+&gt;&gt; 추후에 디테일한 내용은 추가예정
+3. 일정 체크. 
+1주차(26~30)- 기본프로그램이 만들어질 정도
+2주차(11/2~ 6)- 프로그램 세부조정(지연시간 단축, 기술적퀄리티 증가&gt;&gt; 소위 튜닝)
+3주차(11/9~13)- 통합테스트
+4주차(16~20)- 추후 서류 작성
+4. 특이사항,
+- 코테 넣기로(총점에 포함하되, 별도의 점수로 체크.)
+- 2차회의는 2시에 진행
+- 개인공부도 진행은 선택</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+플로우 차트는 공유 드라이브 화면 흐름도에서 확인 가능
+1) 플로우 차트 공유 
+-성준
+- 시나리오 별 플로우 차트
+- 면접중 임의로 세션을 이탈시 초기화되는 악용 경고메세지
+- 오어스를 넣을것인가? 오어스가 존재하되 가입을 먼저해야한다
+- 소현 
+- 대시보드 화면에 처음 들어갔을때 통계적인 화면이 보이는 것보다 공고 화면이 먼저 보이는게 중요하다 통계
+ 화면은 따로 사이드바 쪽으로 해서 따로 배치
+- 그렇게 됐을때 보여지는 화면이 다르기때문에 엔드포인트가 다르다는 우려, 하지만 코드만 달라지기때문에
+ 엔드포인트에 관해서는 괜찮다는 의견
+- AI예상 스코어 제거 
+- 지웅
+- 전체적인 플로우 차트는 기능적인 부분에서 따라가는 방향, 질문을 DB에 넣고 AI 뽑아서 생성하는 방향으로 
+ 플로우 차트 진행
+- 코딩테스트 부분에서 monaco editor를 사용하고 judge0를 사용하는 방식을 채택해서 설명
+- 완료후 어느 화면이 들어오는지에 대한 질문과 메인페이지로 돌아간다는 답변
+- 진희
+- 다양한 플로우 차트 ( 전체플로우, 질문생성 플로우, 챙둉결과 리포트, 코테관련 ) 공유
+- 질문생성 플로우.png에서 관리자 입력질문, DB에 존재하는 질문은행 선택, LLM이 랜덤으로 생성하는 3가지 방식
+ 보여줌 
+ └ 선생님께서 관리자가 수동으로 입력할 질문이 필요한가? AI를 사용하는데 굳이 수동으로 할 필요가 있는지에 
+ 대한 피드백
+- 코딩테스트에 관한 플로우, 함정설계 플로우 부분에서 정보 제한, 오류 유도, 모호한 요구로 함정 설계를 해보는
+ 방안도 어떠냐 라는 제안
+-혜현
+- 답변을 완벽하게 했을때 꼬리질문이 나오지 않고 다음 단계로 진행 
+- 지원자 상세 평가 보기 부분에서 음성 타임라인 하이라이트 플레이어 우수/감점 구간 바로 듣기 기능을 추가해서
+ 플로우 차트를 만들었고 좋다는 반응
+---------------------------------------------------
+2) API 관련 부분
+LLM을 로컬로 다운받아 사용을 할것인가 외부 API를 사용해서 사용할것인가
+- 로컬로 확정
+2.1) 모델 
+LLM모델로는 Qwen, DeepSeek가 존재하며 현재 정해진 모델은 Qwen을 사용할 예정
+Embedding 모델로는 Qwen3 임베딩 모델을 사용할 예정
+TTS - Whisper Large-V3 Turbo 사용할 예정 
+----------------------------------------------------
+3) 역할분담
+- 1차 확정 -&gt; 추후 변경될 가능성이 있음
+└ 질문 분석(이력서/꼬리질문)
+└ 음성 영상
+└ 평가(리포트)
+└ 코딩테스트 
+2 / 1 / 1 / 1 로 나눠서 하자는 의견
+----------------------------------------------------
+4) 이력서 점수 
+- 이력수 점수를 넣어야 하냐는 의견, 넣는걸로 진행을 하기로 했고 추후에 팀원 회의를 통한 변경 가능성 존재
+</t>
+  </si>
+  <si>
+    <t>PRD 각자 생성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26일 (월) PRD, TRD 1차 생성 </t>
+  </si>
+  <si>
+    <t>임베딩 모델이 어디에 쓰이는지에 대한 구체적인 사용처에 대한 모호함.</t>
+  </si>
+  <si>
+    <t>2026-10-16 17:30~ 18:30</t>
+  </si>
+  <si>
+    <t>지원자 페이지 기능들을 어떻게 구현하는지에 대한 회의 / 관리자 페이지 작성하기</t>
+  </si>
+  <si>
+    <t>각 페이지 별 기능들과 우선순위(중요도)를 논의</t>
+  </si>
+  <si>
+    <t>0. 로그인화면이 과연 첫 화면이여야 하는가?
+먼저 공고페이지를 보여주고, 로그인 화면을 선택해서 이동할 수 있게끔 진행하기.
+1. 요구사항 기능정의 표 살펴보기.
+2. 지원자 페이지에 대한 마무리 논의
+(1) 면접완료 안내 페이지 
+- 홈으로 (high) →처음으로 돌아갈 수 있게끔 진행
+- 결과보기(high) →결과리포트 확인하는 버튼 
+- 리포팅 준비중입니다. (high) → 결과보기 활성화되기전 버튼, 나중에 결과보기로 진행하기.
+(2) AI 피드백 페이지
+**방식- 평가항목을 통해서 어떤 기능이 필요한지 가늠하고 체크하기. 중요도는 일단 따로 체크하지 않음.
+☆평가 항목
+질문별 평가(+개념이해도) - 각 질문에 대한 평가 내용. STT된 답변 평가분석 시스템
+논리성- 일관성, 답변의 구체성, 설명의 마무리
+전달력- 말의 속도, 뚜렷함, 음성의 높낮이.
+표현및태도(참여도)- 적극성, 부정적인 단어. 답변시간.
+전문성- 인재상과의 연계 / 회사가치와 맞는지 / 파트에 대한 이해도
+총평- 전체적인 평가 관련된 이야기.  
+총점- 점수 체크하기.
+우선순위 피드백- (좋았던점&lt;강점&gt; -1,2,3순위, 개선점&lt;단점&gt; - 1,2,3순위.)
+이를 위해서 넣어야 하는 기능
+- 시선 트레킹→ 적극성 / 태도와 관련된 부분.
+- 목소리에 대한 높낮이 체크  뚜렷함 등 분석 하는 기능→ 전달력, 참여도
+- STT→ 대화내용을 텍스트로 진행.
+- 감정분석 → 표현및 태도 
+- 답과의 연관성/일관성 분석 →  단어간 벡터 분석
+- 그외 텍스트 분석
+- 답변시간 / 총면접시간
+- AI 평가도구- 텍스트를 통해서 점수를 체크하고 평가하는 시스템.
+3.관리자 페이지 어떤 장면 /기능을 넣을지
+- 로그인 페이지(high)
+- 대시보드(high)
+- 일정관리(high)
+- 면접 질문관리(high)
+- 공고 관리(high)
+- 문의 쪽지(medium)
+4,추후 기능에 대한 이야기
+- UI UX에 관한 이야기.</t>
+  </si>
+  <si>
     <t>2026-10-19 17:30~ 18:30</t>
   </si>
   <si>
@@ -516,7 +667,19 @@
     <t>관리자페이지 기능 구성 마무리</t>
   </si>
   <si>
+    <t>각자 관리자 페이지 어떻게 구성해야할지 고민하기.</t>
+  </si>
+  <si>
     <t>관리자페이지(대시보드, 공고목록, 지원자목록, 질문관리 등..) 기능 구성안 논의</t>
+  </si>
+  <si>
+    <t xml:space="preserve">관리자페이지 기능 구성 과제(다음주월요일까지) PRDTRD 다음주 수요일까지 </t>
+  </si>
+  <si>
+    <t>전문성에 대한 내용들 체크</t>
+  </si>
+  <si>
+    <t>모두 푹 쉬시고 차주 화이팅... 그리고 기능표는 회의록 기준으로 업데이트를 하지만 혹시나 수정할 부분 있으면 이야기해주세요</t>
   </si>
   <si>
     <t>■ 관리자 페이지 기능 (화이트보드 최종안)
@@ -580,6 +743,15 @@
 - 상세 항목: 이력서, 평가 리포트, 항목별 점수, 합격 여부, 질문별 답변, 관리자 메모, 개인 정보(?).</t>
   </si>
   <si>
+    <t>2026-10-15 17:30~ 18:30</t>
+  </si>
+  <si>
+    <t>이진희</t>
+  </si>
+  <si>
+    <t>지원자 페이지 기능들을 어떻게 구현하는지에 대한 회의</t>
+  </si>
+  <si>
     <t>화면정의서 작성</t>
   </si>
   <si>
@@ -590,78 +762,6 @@
 - 이력서 단일 템플릿에 넣을 항목 확정
 - AI 예상 합격 여부의 위치(목록 / 상세) 최종 확인
 - 일정 관리, 면접 질문(가중치) 화면의 세부 기능</t>
-  </si>
-  <si>
-    <t>날씨가 많이 추워졌습니다 모두 몸관리 잘하시고 아프시지 마세용 ㅠㅠ</t>
-  </si>
-  <si>
-    <t>2026-10-16 17:30~ 18:30</t>
-  </si>
-  <si>
-    <t>지원자 페이지 기능들을 어떻게 구현하는지에 대한 회의 / 관리자 페이지 작성하기</t>
-  </si>
-  <si>
-    <t>각 페이지 별 기능들과 우선순위(중요도)를 논의</t>
-  </si>
-  <si>
-    <t>0. 로그인화면이 과연 첫 화면이여야 하는가?
-먼저 공고페이지를 보여주고, 로그인 화면을 선택해서 이동할 수 있게끔 진행하기.
-1. 요구사항 기능정의 표 살펴보기.
-2. 지원자 페이지에 대한 마무리 논의
-(1) 면접완료 안내 페이지 
-- 홈으로 (high) →처음으로 돌아갈 수 있게끔 진행
-- 결과보기(high) →결과리포트 확인하는 버튼 
-- 리포팅 준비중입니다. (high) → 결과보기 활성화되기전 버튼, 나중에 결과보기로 진행하기.
-(2) AI 피드백 페이지
-**방식- 평가항목을 통해서 어떤 기능이 필요한지 가늠하고 체크하기. 중요도는 일단 따로 체크하지 않음.
-☆평가 항목
-질문별 평가(+개념이해도) - 각 질문에 대한 평가 내용. STT된 답변 평가분석 시스템
-논리성- 일관성, 답변의 구체성, 설명의 마무리
-전달력- 말의 속도, 뚜렷함, 음성의 높낮이.
-표현및태도(참여도)- 적극성, 부정적인 단어. 답변시간.
-전문성- 인재상과의 연계 / 회사가치와 맞는지 / 파트에 대한 이해도
-총평- 전체적인 평가 관련된 이야기.  
-총점- 점수 체크하기.
-우선순위 피드백- (좋았던점&lt;강점&gt; -1,2,3순위, 개선점&lt;단점&gt; - 1,2,3순위.)
-이를 위해서 넣어야 하는 기능
-- 시선 트레킹→ 적극성 / 태도와 관련된 부분.
-- 목소리에 대한 높낮이 체크  뚜렷함 등 분석 하는 기능→ 전달력, 참여도
-- STT→ 대화내용을 텍스트로 진행.
-- 감정분석 → 표현및 태도 
-- 답과의 연관성/일관성 분석 →  단어간 벡터 분석
-- 그외 텍스트 분석
-- 답변시간 / 총면접시간
-- AI 평가도구- 텍스트를 통해서 점수를 체크하고 평가하는 시스템.
-3.관리자 페이지 어떤 장면 /기능을 넣을지
-- 로그인 페이지(high)
-- 대시보드(high)
-- 일정관리(high)
-- 면접 질문관리(high)
-- 공고 관리(high)
-- 문의 쪽지(medium)
-4,추후 기능에 대한 이야기
-- UI UX에 관한 이야기.</t>
-  </si>
-  <si>
-    <t>각자 관리자 페이지 어떻게 구성해야할지 고민하기.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">관리자페이지 기능 구성 과제(다음주월요일까지) PRDTRD 다음주 수요일까지 </t>
-  </si>
-  <si>
-    <t>2026-10-15 17:30~ 18:30</t>
-  </si>
-  <si>
-    <t>전문성에 대한 내용들 체크</t>
-  </si>
-  <si>
-    <t>모두 푹 쉬시고 차주 화이팅... 그리고 기능표는 회의록 기준으로 업데이트를 하지만 혹시나 수정할 부분 있으면 이야기해주세요</t>
-  </si>
-  <si>
-    <t>이진희</t>
-  </si>
-  <si>
-    <t>지원자 페이지 기능들을 어떻게 구현하는지에 대한 회의</t>
   </si>
   <si>
     <t>**지난 회의에 이어서 진행.**
@@ -720,25 +820,28 @@
 결정되면 자신들이 UX/UI를 제작해서 보여주면 좋을거 같단 생각&gt;&gt; 해당 부분은 금요일에 검토</t>
   </si>
   <si>
+    <t>날씨가 많이 추워졌습니다 모두 몸관리 잘하시고 아프시지 마세용 ㅠㅠ</t>
+  </si>
+  <si>
+    <t>관리자페이지 기능 / 지원자페이지 기능 마무리 / PRDTRD</t>
+  </si>
+  <si>
+    <t>PRDTRD 담주 수요일까지.</t>
+  </si>
+  <si>
+    <t>코딩테스트 관련 프로그램. 질문에 대한 내용 체크하기</t>
+  </si>
+  <si>
     <t>자세한 것은 공유파일 참고</t>
   </si>
   <si>
-    <t>관리자페이지 기능 / 지원자페이지 기능 마무리 / PRDTRD</t>
-  </si>
-  <si>
-    <t>PRDTRD 담주 수요일까지.</t>
-  </si>
-  <si>
-    <t>코딩테스트 관련 프로그램. 질문에 대한 내용 체크하기</t>
-  </si>
-  <si>
     <t>진헤라 죄송합니다.</t>
   </si>
   <si>
+    <t>오늘 다들 고생하셨습니다, 기능 정리 표는 구글드라이브 초안/정리 자료 폴더에 넣어놓겠습니다.</t>
+  </si>
+  <si>
     <t>2026-10-14 17:00~ 18:28</t>
-  </si>
-  <si>
-    <t>오늘 다들 고생하셨습니다, 기능 정리 표는 구글드라이브 초안/정리 자료 폴더에 넣어놓겠습니다.</t>
   </si>
   <si>
     <t>면접 절차에 대한 전체적인 흐름을 팀원들이 파악/공유하고, 각 페이지에 어떤 기능을 넣을지에 대한 논의</t>
@@ -819,6 +922,9 @@
     <t>실질적으로 이 기능을 넣는게 유의미한가에 대한 논의를 많이함.</t>
   </si>
   <si>
+    <t>시장조사 및 개요 회의</t>
+  </si>
+  <si>
     <t>0. 와이어프레임 공유(지웅/ 성준)
 1. 명칭 통일
 관리자 / 담당자 / 지원자
@@ -848,34 +954,28 @@
 지원자가 선택? 사실이게 의미가 있는 것인가.</t>
   </si>
   <si>
+    <t>시작 설계 회의</t>
+  </si>
+  <si>
+    <t>2026.10.08  17:30~18:33</t>
+  </si>
+  <si>
     <t>PRD/TRD 작성(다음주 수요일까지) / 기능 관련 회의 종료 (금요일까지)</t>
   </si>
   <si>
+    <t xml:space="preserve">시장조사 / 개요 </t>
+  </si>
+  <si>
     <t xml:space="preserve">기능회의 계속 이어서 진행하기. </t>
   </si>
   <si>
+    <t>PRD / TRD만들기 전 회의</t>
+  </si>
+  <si>
     <t>실질적으로 제대로 효용성이 있는 면접이 될 수 있게끔 하는 것. 지원자 / 담당자가 만족을 할 수 있는 '기본'기능을 구현하고 추가 기능을 통해서 차별성을 높이는 것이 중요.</t>
   </si>
   <si>
     <t>혹시라도 틀리거나 곡해된 부분이나, 이상한 부분 있으면 꼭 말씀해주세요.</t>
-  </si>
-  <si>
-    <t>팀장님 코멘트 올려주시면 감사합니다.(사실 이걸로 보시는지 체크하고있어요.)</t>
-  </si>
-  <si>
-    <t>시장조사 및 개요 회의</t>
-  </si>
-  <si>
-    <t>시작 설계 회의</t>
-  </si>
-  <si>
-    <t>2026.10.08  17:30~18:33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시장조사 / 개요 </t>
-  </si>
-  <si>
-    <t>PRD / TRD만들기 전 회의</t>
   </si>
   <si>
     <t>시장조사 관련 느낀점 말하기-성준, 지웅
@@ -909,16 +1009,19 @@
 4. 해야할 일, 모의면접에 대해서 한번 고민해보자.</t>
   </si>
   <si>
+    <t>팀장님 코멘트 올려주시면 감사합니다.(사실 이걸로 보시는지 체크하고있어요.)</t>
+  </si>
+  <si>
     <t>모의면접/실전면접에 관한 고민 / 면접관페르소나</t>
   </si>
   <si>
     <t>10월 16일까지 PRD TRD작성(아직 미정)</t>
   </si>
   <si>
+    <t>모의면접 / 실전면접</t>
+  </si>
+  <si>
     <t>시장조사 회의</t>
-  </si>
-  <si>
-    <t>모의면접 / 실전면접</t>
   </si>
   <si>
     <t>조사후 결과보고</t>
@@ -975,9 +1078,6 @@
   </si>
   <si>
     <t>진행 시 역할 분담에 관한 내용과 파일 및 일정관리에 대한 내용</t>
-  </si>
-  <si>
-    <t>AI 모의면접 실제로 해보기</t>
   </si>
   <si>
     <t xml:space="preserve">안건 1. 
@@ -1014,6 +1114,21 @@
 </t>
   </si>
   <si>
+    <t>시장조사, 엑셀로 정리하기, 결과물에 대한 논의</t>
+  </si>
+  <si>
+    <t>시장조사(~10/5)</t>
+  </si>
+  <si>
+    <t>프로젝트명, 역할분담</t>
+  </si>
+  <si>
+    <t>냉무, 연휴 잘보내시길</t>
+  </si>
+  <si>
+    <t>AI 모의면접 실제로 해보기</t>
+  </si>
+  <si>
     <t>이후 행동에 대한 설계</t>
   </si>
   <si>
@@ -1023,22 +1138,10 @@
     <t>지웅, 소현, 진희, 혜현, 성준</t>
   </si>
   <si>
-    <t>시장조사, 엑셀로 정리하기, 결과물에 대한 논의</t>
-  </si>
-  <si>
-    <t>시장조사(~10/5)</t>
-  </si>
-  <si>
     <t>AI 모의면접 조사 기획</t>
   </si>
   <si>
     <t>어떤 회사의 AI모의면접을 할지 고민해보고 결정하기</t>
-  </si>
-  <si>
-    <t>프로젝트명, 역할분담</t>
-  </si>
-  <si>
-    <t>냉무, 연휴 잘보내시길</t>
   </si>
   <si>
     <t>1. 각자 사람in사이트에 있는 모의면접은 진행해보기(예외 : 소현은 외국 사이트를 다루고 있기 때문에, 거기에 집중)
@@ -1296,6 +1399,10 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1307,7 +1414,7 @@
     <xdr:ext cx="6705600" cy="5629275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image14.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image22.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1335,7 +1442,7 @@
     <xdr:ext cx="6743700" cy="4695825"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image17.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1356,7 +1463,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1368,7 +1475,7 @@
     <xdr:ext cx="6286500" cy="3867150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image26.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1396,7 +1503,7 @@
     <xdr:ext cx="5819775" cy="3371850"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image21.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image28.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1424,7 +1531,7 @@
     <xdr:ext cx="5962650" cy="2419350"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image23.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image19.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1452,7 +1559,7 @@
     <xdr:ext cx="5419725" cy="3314700"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image10.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1480,7 +1587,7 @@
     <xdr:ext cx="6791325" cy="4953000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image25.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image18.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1508,7 +1615,7 @@
     <xdr:ext cx="6753225" cy="4953000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image13.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1536,7 +1643,7 @@
     <xdr:ext cx="6286500" cy="3095625"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image17.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image6.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1564,7 +1671,7 @@
     <xdr:ext cx="962025" cy="552450"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image22.png"/>
+        <xdr:cNvPr id="0" name="image27.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1585,10 +1692,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
@@ -1598,6 +1701,10 @@
 </file>
 
 <file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1609,7 +1716,7 @@
     <xdr:ext cx="7496175" cy="2400300"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image8.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image26.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1630,11 +1737,11 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1646,7 +1753,7 @@
     <xdr:ext cx="3505200" cy="2190750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image11.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image5.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1674,7 +1781,7 @@
     <xdr:ext cx="3895725" cy="2438400"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image20.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image21.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1702,7 +1809,7 @@
     <xdr:ext cx="4029075" cy="2514600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image10.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1730,7 +1837,7 @@
     <xdr:ext cx="314325" cy="200025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image27.png"/>
+        <xdr:cNvPr id="0" name="image23.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1751,7 +1858,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1763,7 +1870,7 @@
     <xdr:ext cx="3333750" cy="3343275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image9.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image12.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1791,7 +1898,7 @@
     <xdr:ext cx="3343275" cy="3343275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image7.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image11.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1819,7 +1926,7 @@
     <xdr:ext cx="2581275" cy="2581275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image18.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image7.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1847,7 +1954,7 @@
     <xdr:ext cx="2743200" cy="1371600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image19.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image9.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1903,7 +2010,7 @@
     <xdr:ext cx="2190750" cy="1819275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image12.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image4.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1937,6 +2044,10 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1948,7 +2059,7 @@
     <xdr:ext cx="1819275" cy="3714750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image15.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image24.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1976,7 +2087,7 @@
     <xdr:ext cx="2105025" cy="3714750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image24.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image25.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2004,7 +2115,7 @@
     <xdr:ext cx="1819275" cy="3571875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image13.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2032,7 +2143,7 @@
     <xdr:ext cx="3143250" cy="3371850"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image8.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2060,7 +2171,7 @@
     <xdr:ext cx="1743075" cy="4295775"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image14.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2081,7 +2192,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -2093,7 +2204,7 @@
     <xdr:ext cx="6600825" cy="2981325"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image15.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2114,11 +2225,11 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -2130,7 +2241,7 @@
     <xdr:ext cx="6734175" cy="5438775"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image28.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image20.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2149,10 +2260,6 @@
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2378,43 +2485,43 @@
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4"/>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4"/>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4"/>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4"/>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4"/>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4"/>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6"/>
     </row>
@@ -2424,31 +2531,31 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4"/>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -2512,63 +2619,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -2577,42 +2684,40 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>93</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16">
@@ -2660,7 +2765,6 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="13.88"/>
     <col customWidth="1" min="3" max="3" width="95.88"/>
   </cols>
   <sheetData>
@@ -2676,68 +2780,64 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="P9" s="13"/>
+        <v>24</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
       <c r="B10" s="7"/>
@@ -2745,7 +2845,7 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>98</v>
@@ -2753,7 +2853,7 @@
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>99</v>
@@ -2761,7 +2861,7 @@
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>100</v>
@@ -2769,18 +2869,18 @@
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16">
@@ -2828,6 +2928,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="2" max="2" width="13.88"/>
     <col customWidth="1" min="3" max="3" width="95.88"/>
   </cols>
   <sheetData>
@@ -2843,64 +2944,68 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>106</v>
       </c>
+      <c r="P9" s="13"/>
     </row>
     <row r="10" ht="306.75" customHeight="1">
       <c r="B10" s="7"/>
@@ -2908,7 +3013,7 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>107</v>
@@ -2916,7 +3021,7 @@
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>108</v>
@@ -2924,7 +3029,7 @@
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>109</v>
@@ -2932,7 +3037,7 @@
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>110</v>
@@ -2940,7 +3045,7 @@
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>111</v>
@@ -3006,63 +3111,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>112</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -3071,39 +3176,43 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="9"/>
+        <v>39</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="1"/>
@@ -3165,63 +3274,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -3230,7 +3339,7 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>127</v>
@@ -3238,7 +3347,7 @@
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>128</v>
@@ -3246,7 +3355,7 @@
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>129</v>
@@ -3254,15 +3363,13 @@
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>130</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -3326,20 +3433,20 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>132</v>
@@ -3347,42 +3454,42 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -3391,39 +3498,39 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -3487,44 +3594,44 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>138</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>143</v>
@@ -3532,7 +3639,7 @@
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>144</v>
@@ -3540,10 +3647,10 @@
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -3552,39 +3659,39 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -3648,64 +3755,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="H2" s="13"/>
+        <v>150</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -3714,39 +3820,39 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -3810,20 +3916,21 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>162</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="H2" s="13"/>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>163</v>
@@ -3831,42 +3938,42 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -3875,39 +3982,200 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
+      </c>
+      <c r="C15" s="9"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="H2:N15"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="95.88"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="H1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" ht="439.5" customHeight="1">
+      <c r="B9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" ht="306.75" customHeight="1">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -3971,28 +4239,28 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>12</v>
@@ -4000,34 +4268,34 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -4036,33 +4304,33 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>21</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C12" s="4"/>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -4126,63 +4394,66 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>22</v>
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -4191,35 +4462,33 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>35</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C11" s="4"/>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -4283,66 +4552,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -4351,41 +4617,37 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>40</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="C13" s="4"/>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>41</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C15" s="9"/>
     </row>
     <row r="16">
       <c r="B16" s="1"/>
@@ -4447,63 +4709,66 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -4512,39 +4777,41 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="9"/>
+        <v>39</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="1"/>
@@ -4606,63 +4873,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -4671,31 +4938,37 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -4759,63 +5032,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -4824,37 +5097,31 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C11" s="4"/>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C12" s="4"/>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="C13" s="4"/>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -4918,63 +5185,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -4983,41 +5250,39 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>76</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C15" s="9"/>
     </row>
     <row r="16">
       <c r="B16" s="1"/>
@@ -5079,63 +5344,63 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" ht="439.5" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" ht="306.75" customHeight="1">
@@ -5144,40 +5409,40 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
